--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822242903676129"/>
-          <c:y val="0.0667195614541258"/>
-          <c:w val="0.70544439274081"/>
-          <c:h val="0.857905366416619"/>
+          <c:x val="0.0822319434102755"/>
+          <c:y val="0.0667291877074015"/>
+          <c:w val="0.705416976917349"/>
+          <c:h val="0.857740585774059"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -365,7 +365,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Monday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Sunday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,25 +435,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>78.7</c:v>
+                  <c:v>77.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>77.7</c:v>
+                  <c:v>77.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>76.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76.4</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>77.5</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>77.1</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>76.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>76.4</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>77.5</c:v>
+                  <c:v>78.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -476,11 +476,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FF420E"/>
+              <a:srgbClr val="ff420e"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -490,7 +490,7 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -500,7 +500,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Monday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Sunday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>77.1142857142857</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>77.1857142857143</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>77.1333333333333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77.14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>77.3</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>77.6</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.3428571428571</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>77.1166666666667</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>77</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>76.875</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>76.8</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.95</c:v>
+                  <c:v>77.65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="54929865"/>
-        <c:axId val="85379013"/>
+        <c:axId val="31802415"/>
+        <c:axId val="53724173"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="54929865"/>
+        <c:axId val="31802415"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -620,7 +620,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -629,7 +629,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85379013"/>
+        <c:crossAx val="53724173"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85379013"/>
+        <c:axId val="53724173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -658,7 +658,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:srgbClr val="b3b3b3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -670,7 +670,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -679,7 +679,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54929865"/>
+        <c:crossAx val="31802415"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -698,7 +698,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
+            <a:srgbClr val="b3b3b3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -727,7 +727,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -744,7 +744,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0821815812741403"/>
-          <c:y val="0.0667388167388167"/>
-          <c:w val="0.705477220903718"/>
-          <c:h val="0.857936507936508"/>
+          <c:x val="0.0821892306976311"/>
+          <c:y val="0.0667484485495743"/>
+          <c:w val="0.705449806859962"/>
+          <c:h val="0.857771684225718"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -803,7 +803,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -903,11 +903,11 @@
           <c:order val="1"/>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FF420E"/>
+              <a:srgbClr val="ff420e"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -917,7 +917,7 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -927,7 +927,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="59374226"/>
-        <c:axId val="93826325"/>
+        <c:axId val="8635947"/>
+        <c:axId val="70929083"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="59374226"/>
+        <c:axId val="8635947"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1047,7 +1047,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1056,7 +1056,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93826325"/>
+        <c:crossAx val="70929083"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="93826325"/>
+        <c:axId val="70929083"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1085,7 +1085,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:srgbClr val="b3b3b3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1097,7 +1097,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1106,7 +1106,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="59374226"/>
+        <c:crossAx val="8635947"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1125,7 +1125,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
+            <a:srgbClr val="b3b3b3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -1154,7 +1154,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1171,449 +1171,13 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1627,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>683280</xdr:colOff>
+      <xdr:colOff>682560</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>179280</xdr:rowOff>
+      <xdr:rowOff>178560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1638,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7736040" cy="4990680"/>
+        <a:ext cx="7735320" cy="4989960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1662,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>70200</xdr:colOff>
+      <xdr:colOff>69480</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>188640</xdr:rowOff>
+      <xdr:rowOff>187920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1673,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7735680" cy="4989240"/>
+        <a:ext cx="7734960" cy="4988520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1694,37 +1258,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1840,15 +1404,15 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>78.7</v>
+        <v>77.5</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.6</v>
+        <v>77.1142857142857</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1880,15 +1444,15 @@
       </c>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.7</v>
+        <v>77.1</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.3428571428571</v>
+        <v>77.1857142857143</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1920,15 +1484,15 @@
       </c>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.5</v>
+        <v>76.5</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1166666666667</v>
+        <v>77.1333333333333</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1963,19 +1527,19 @@
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>77.5</v>
+        <v>77.1</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46079</v>
+        <v>46081</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>76.4</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2010,19 +1574,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>77.3428571428571</v>
+        <v>77.1857142857143</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46080</v>
+        <v>46082</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.5</v>
+        <v>77.5</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.875</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2055,15 +1619,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>77.1</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.8</v>
+        <v>77.6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2101,15 +1665,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46082</v>
+        <v>46084</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.5</v>
+        <v>78.2</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.95</v>
+        <v>77.65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2212,7 +1776,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>51.4</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2386,7 +1950,7 @@
       </c>
       <c r="G16" s="7" t="n">
         <f aca="false">AVERAGE(B15:B21)</f>
-        <v>77.1166666666667</v>
+        <v>77.1142857142857</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2414,7 +1978,7 @@
       </c>
       <c r="G17" s="7" t="n">
         <f aca="false">AVERAGE(B16:B22)</f>
-        <v>77</v>
+        <v>77.1857142857143</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2442,7 +2006,7 @@
       </c>
       <c r="G18" s="7" t="n">
         <f aca="false">AVERAGE(B17:B23)</f>
-        <v>76.875</v>
+        <v>77.1333333333333</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2470,7 +2034,7 @@
       </c>
       <c r="G19" s="7" t="n">
         <f aca="false">AVERAGE(B18:B24)</f>
-        <v>76.8</v>
+        <v>77.14</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>8</v>
@@ -2501,24 +2065,27 @@
       </c>
       <c r="G20" s="7" t="n">
         <f aca="false">AVERAGE(B19:B25)</f>
-        <v>76.95</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="n">
         <v>46083</v>
       </c>
+      <c r="B21" s="1" t="n">
+        <v>77.1</v>
+      </c>
       <c r="C21" s="11" t="n">
         <f aca="false">B21-B20</f>
-        <v>-77.5</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D21" s="3" t="n">
         <f aca="false">B21*2.204623</f>
-        <v>0</v>
+        <v>169.9764333</v>
       </c>
       <c r="E21" s="7" t="n">
         <f aca="false">C21*2.204623</f>
-        <v>-170.8582825</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F21" s="4" t="n">
         <f aca="false">A21</f>
@@ -2526,32 +2093,35 @@
       </c>
       <c r="G21" s="7" t="n">
         <f aca="false">AVERAGE(B20:B26)</f>
-        <v>77.5</v>
+        <v>77.6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="n">
         <v>46084</v>
       </c>
+      <c r="B22" s="1" t="n">
+        <v>78.2</v>
+      </c>
       <c r="C22" s="11" t="n">
         <f aca="false">B22-B21</f>
-        <v>0</v>
+        <v>1.10000000000001</v>
       </c>
       <c r="D22" s="3" t="n">
         <f aca="false">B22*2.204623</f>
-        <v>0</v>
+        <v>172.4015186</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">C22*2.204623</f>
-        <v>0</v>
+        <v>2.42508530000002</v>
       </c>
       <c r="F22" s="4" t="n">
         <f aca="false">A22</f>
         <v>46084</v>
       </c>
-      <c r="G22" s="7" t="e">
+      <c r="G22" s="7" t="n">
         <f aca="false">AVERAGE(B21:B27)</f>
-        <v>#DIV/0!</v>
+        <v>77.65</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,7 +2130,7 @@
       </c>
       <c r="C23" s="11" t="n">
         <f aca="false">B23-B22</f>
-        <v>0</v>
+        <v>-78.2</v>
       </c>
       <c r="D23" s="3" t="n">
         <f aca="false">B23*2.204623</f>
@@ -2568,15 +2138,15 @@
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">C23*2.204623</f>
-        <v>0</v>
+        <v>-172.4015186</v>
       </c>
       <c r="F23" s="4" t="n">
         <f aca="false">A23</f>
         <v>46085</v>
       </c>
-      <c r="G23" s="7" t="e">
+      <c r="G23" s="7" t="n">
         <f aca="false">AVERAGE(B22:B28)</f>
-        <v>#DIV/0!</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822319434102755"/>
-          <c:y val="0.0667291877074015"/>
-          <c:w val="0.705416976917349"/>
-          <c:h val="0.857740585774059"/>
+          <c:x val="0.0822434256457994"/>
+          <c:y val="0.0667436322967025"/>
+          <c:w val="0.705375843611822"/>
+          <c:h val="0.85749332563677"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Wednesday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Tuesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,25 +435,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>76.4</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>77.5</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>77.1</c:v>
                 </c:pt>
-                <c:pt idx="2">
-                  <c:v>76.5</c:v>
-                </c:pt>
                 <c:pt idx="3">
+                  <c:v>78.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>77.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>76.4</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>77.5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>77.1</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>78.2</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Wednesday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Tuesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>77.1142857142857</c:v>
+                  <c:v>77.1285714285714</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>77.1857142857143</c:v>
+                  <c:v>77.0571428571429</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77.1333333333333</c:v>
+                  <c:v>77.1666666666667</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.14</c:v>
+                  <c:v>77.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.3</c:v>
+                  <c:v>77.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>77.6</c:v>
+                  <c:v>76.7333333333333</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>77.65</c:v>
+                  <c:v>76.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="31802415"/>
-        <c:axId val="53724173"/>
+        <c:axId val="11362220"/>
+        <c:axId val="15938252"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="31802415"/>
+        <c:axId val="11362220"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53724173"/>
+        <c:crossAx val="15938252"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53724173"/>
+        <c:axId val="15938252"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31802415"/>
+        <c:crossAx val="11362220"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0821892306976311"/>
-          <c:y val="0.0667484485495743"/>
-          <c:w val="0.705449806859962"/>
-          <c:h val="0.857771684225718"/>
+          <c:x val="0.0822007075032582"/>
+          <c:y val="0.0667629014796103"/>
+          <c:w val="0.705408676224167"/>
+          <c:h val="0.857524359437026"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="8635947"/>
-        <c:axId val="70929083"/>
+        <c:axId val="9710084"/>
+        <c:axId val="5419366"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="8635947"/>
+        <c:axId val="9710084"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70929083"/>
+        <c:crossAx val="5419366"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70929083"/>
+        <c:axId val="5419366"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="8635947"/>
+        <c:crossAx val="9710084"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1191,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>682560</xdr:colOff>
+      <xdr:colOff>681480</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>178560</xdr:rowOff>
+      <xdr:rowOff>177480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7735320" cy="4989960"/>
+        <a:ext cx="7734240" cy="4988880"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1226,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>69480</xdr:colOff>
+      <xdr:colOff>68400</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>187920</xdr:rowOff>
+      <xdr:rowOff>186840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1237,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7734960" cy="4988520"/>
+        <a:ext cx="7733880" cy="4987440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1404,15 +1404,15 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46078</v>
+        <v>46081</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.5</v>
+        <v>76.4</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1142857142857</v>
+        <v>77.1285714285714</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1444,15 +1444,15 @@
       </c>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46079</v>
+        <v>46082</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>77.5</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1857142857143</v>
+        <v>77.0571428571429</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1484,15 +1484,15 @@
       </c>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.5</v>
+        <v>77.1</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1333333333333</v>
+        <v>77.1666666666667</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1531,15 +1531,15 @@
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46081</v>
+        <v>46084</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>78.2</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.14</v>
+        <v>77.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1574,19 +1574,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>77.1857142857143</v>
+        <v>77.0571428571429</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46082</v>
+        <v>46085</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.3</v>
+        <v>77.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1619,15 +1619,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>76.4</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.6</v>
+        <v>76.7333333333333</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1665,15 +1665,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>78.2</v>
+        <v>76</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.65</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>50.3</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="G18" s="7" t="n">
         <f aca="false">AVERAGE(B17:B23)</f>
-        <v>77.1333333333333</v>
+        <v>77.2285714285714</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="G19" s="7" t="n">
         <f aca="false">AVERAGE(B18:B24)</f>
-        <v>77.14</v>
+        <v>77.1285714285714</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>8</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="G20" s="7" t="n">
         <f aca="false">AVERAGE(B19:B25)</f>
-        <v>77.3</v>
+        <v>77.0571428571429</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="G21" s="7" t="n">
         <f aca="false">AVERAGE(B20:B26)</f>
-        <v>77.6</v>
+        <v>77.1666666666667</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2121,24 +2121,27 @@
       </c>
       <c r="G22" s="7" t="n">
         <f aca="false">AVERAGE(B21:B27)</f>
-        <v>77.65</v>
+        <v>77.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="n">
         <v>46085</v>
       </c>
+      <c r="B23" s="1" t="n">
+        <v>77.8</v>
+      </c>
       <c r="C23" s="11" t="n">
         <f aca="false">B23-B22</f>
-        <v>-78.2</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D23" s="3" t="n">
         <f aca="false">B23*2.204623</f>
-        <v>0</v>
+        <v>171.5196694</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">C23*2.204623</f>
-        <v>-172.4015186</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F23" s="4" t="n">
         <f aca="false">A23</f>
@@ -2146,57 +2149,63 @@
       </c>
       <c r="G23" s="7" t="n">
         <f aca="false">AVERAGE(B22:B28)</f>
-        <v>78.2</v>
+        <v>77.1</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>46086</v>
       </c>
+      <c r="B24" s="1" t="n">
+        <v>76.4</v>
+      </c>
       <c r="C24" s="11" t="n">
         <f aca="false">B24-B23</f>
-        <v>0</v>
+        <v>-1.39999999999999</v>
       </c>
       <c r="D24" s="3" t="n">
         <f aca="false">B24*2.204623</f>
-        <v>0</v>
+        <v>168.4331972</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">C24*2.204623</f>
-        <v>0</v>
+        <v>-3.08647219999998</v>
       </c>
       <c r="F24" s="4" t="n">
         <f aca="false">A24</f>
         <v>46086</v>
       </c>
-      <c r="G24" s="7" t="e">
+      <c r="G24" s="7" t="n">
         <f aca="false">AVERAGE(B23:B29)</f>
-        <v>#DIV/0!</v>
+        <v>76.7333333333333</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="n">
         <v>46087</v>
       </c>
+      <c r="B25" s="1" t="n">
+        <v>76</v>
+      </c>
       <c r="C25" s="11" t="n">
         <f aca="false">B25-B24</f>
-        <v>0</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D25" s="3" t="n">
         <f aca="false">B25*2.204623</f>
-        <v>0</v>
+        <v>167.551348</v>
       </c>
       <c r="E25" s="7" t="n">
         <f aca="false">C25*2.204623</f>
-        <v>0</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F25" s="4" t="n">
         <f aca="false">A25</f>
         <v>46087</v>
       </c>
-      <c r="G25" s="7" t="e">
+      <c r="G25" s="7" t="n">
         <f aca="false">AVERAGE(B24:B30)</f>
-        <v>#DIV/0!</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2205,7 +2214,7 @@
       </c>
       <c r="C26" s="11" t="n">
         <f aca="false">B26-B25</f>
-        <v>0</v>
+        <v>-76</v>
       </c>
       <c r="D26" s="3" t="n">
         <f aca="false">B26*2.204623</f>
@@ -2213,15 +2222,15 @@
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">C26*2.204623</f>
-        <v>0</v>
+        <v>-167.551348</v>
       </c>
       <c r="F26" s="4" t="n">
         <f aca="false">A26</f>
         <v>46088</v>
       </c>
-      <c r="G26" s="7" t="e">
+      <c r="G26" s="7" t="n">
         <f aca="false">AVERAGE(B25:B31)</f>
-        <v>#DIV/0!</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822434256457994"/>
-          <c:y val="0.0667436322967025"/>
-          <c:w val="0.705375843611822"/>
-          <c:h val="0.85749332563677"/>
+          <c:x val="0.0822510822510823"/>
+          <c:y val="0.0667532654975825"/>
+          <c:w val="0.705348415025834"/>
+          <c:h val="0.857328426066248"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -365,7 +365,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Saturday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Friday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,25 +435,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>77.1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>78.2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>77.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>76.4</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>77.5</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>77.1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>78.2</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.8</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.4</c:v>
+                  <c:v>75.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -476,11 +476,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="FF420E"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -490,7 +490,7 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -500,7 +500,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Saturday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Friday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>77.1285714285714</c:v>
+                  <c:v>77.3125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>77.0571428571429</c:v>
+                  <c:v>77.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77.1666666666667</c:v>
+                  <c:v>77.2625</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.1</c:v>
+                  <c:v>77.125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.1</c:v>
+                  <c:v>76.9875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.7333333333333</c:v>
+                  <c:v>76.9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.2</c:v>
+                  <c:v>76.975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="11362220"/>
-        <c:axId val="15938252"/>
+        <c:axId val="14905714"/>
+        <c:axId val="3933243"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="11362220"/>
+        <c:axId val="14905714"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -620,7 +620,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -629,7 +629,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="15938252"/>
+        <c:crossAx val="3933243"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="15938252"/>
+        <c:axId val="3933243"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -658,7 +658,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -670,7 +670,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -679,7 +679,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11362220"/>
+        <c:crossAx val="14905714"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -698,7 +698,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -727,7 +727,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -744,7 +744,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822007075032582"/>
-          <c:y val="0.0667629014796103"/>
-          <c:w val="0.705408676224167"/>
-          <c:h val="0.857524359437026"/>
+          <c:x val="0.0822083604878503"/>
+          <c:y val="0.0667725402439905"/>
+          <c:w val="0.705381249418118"/>
+          <c:h val="0.857359416732838"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -803,7 +803,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -903,11 +903,11 @@
           <c:order val="1"/>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="FF420E"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -917,7 +917,7 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -927,7 +927,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="9710084"/>
-        <c:axId val="5419366"/>
+        <c:axId val="69284205"/>
+        <c:axId val="55093696"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="9710084"/>
+        <c:axId val="69284205"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1047,7 +1047,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1056,7 +1056,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5419366"/>
+        <c:crossAx val="55093696"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5419366"/>
+        <c:axId val="55093696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1085,7 +1085,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
+                <a:srgbClr val="B3B3B3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1097,7 +1097,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
+              <a:srgbClr val="B3B3B3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1106,7 +1106,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9710084"/>
+        <c:crossAx val="69284205"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1125,7 +1125,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="b3b3b3"/>
+            <a:srgbClr val="B3B3B3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -1154,7 +1154,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1171,13 +1171,449 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:lineWidthScale>1</cs:lineWidthScale>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+    <a:defRPr sz="1800" b="0"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:lineWidthScale>1</cs:lineWidthScale>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+    <a:defRPr sz="1800" b="0"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1191,9 +1627,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>681480</xdr:colOff>
+      <xdr:colOff>680760</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>177480</xdr:rowOff>
+      <xdr:rowOff>176760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1638,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7734240" cy="4988880"/>
+        <a:ext cx="7733520" cy="4988160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1226,9 +1662,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>68400</xdr:colOff>
+      <xdr:colOff>67680</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>186840</xdr:rowOff>
+      <xdr:rowOff>186120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1237,7 +1673,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7733880" cy="4987440"/>
+        <a:ext cx="7733160" cy="4986720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1258,37 +1694,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1404,15 +1840,15 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46081</v>
+        <v>46083</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>77.1</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1285714285714</v>
+        <v>77.3125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1438,21 +1874,18 @@
         <f aca="false">A2</f>
         <v>46064</v>
       </c>
-      <c r="G2" s="7" t="n">
-        <f aca="false">AVERAGE(B1:B7)</f>
-        <v>77.5142857142857</v>
-      </c>
+      <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46082</v>
+        <v>46084</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.5</v>
+        <v>78.2</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.0571428571429</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,21 +1911,18 @@
         <f aca="false">A3</f>
         <v>46065</v>
       </c>
-      <c r="G3" s="7" t="n">
-        <f aca="false">AVERAGE(B2:B8)</f>
-        <v>77.1142857142857</v>
-      </c>
+      <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>77.8</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1666666666667</v>
+        <v>77.2625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,28 +1948,25 @@
         <f aca="false">A4</f>
         <v>46066</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <f aca="false">AVERAGE(B3:B9)</f>
-        <v>76.7714285714286</v>
-      </c>
+      <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>77.1</v>
+        <v>77</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>78.2</v>
+        <v>76.4</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>77.125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1565,28 +1992,25 @@
         <f aca="false">A5</f>
         <v>46067</v>
       </c>
-      <c r="G5" s="7" t="n">
-        <f aca="false">AVERAGE(B4:B10)</f>
-        <v>76.8714285714286</v>
-      </c>
+      <c r="G5" s="7"/>
       <c r="H5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>77.0571428571429</v>
+        <v>76.9</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.8</v>
+        <v>76</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>76.9875</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1612,22 +2036,19 @@
         <f aca="false">A6</f>
         <v>46068</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <f aca="false">AVERAGE(B5:B11)</f>
-        <v>77.0428571428571</v>
-      </c>
+      <c r="G6" s="7"/>
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46086</v>
+        <v>46088</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>75.8</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.7333333333333</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1653,10 +2074,7 @@
         <f aca="false">A7</f>
         <v>46069</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <f aca="false">AVERAGE(B6:B12)</f>
-        <v>77.3</v>
-      </c>
+      <c r="G7" s="7"/>
       <c r="H7" s="6" t="s">
         <v>4</v>
       </c>
@@ -1665,15 +2083,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46087</v>
+        <v>46089</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.2</v>
+        <v>76.975</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1699,10 +2117,7 @@
         <f aca="false">A8</f>
         <v>46070</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <f aca="false">AVERAGE(B7:B13)</f>
-        <v>77.6857142857143</v>
-      </c>
+      <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="n">
@@ -1728,8 +2143,8 @@
         <v>46071</v>
       </c>
       <c r="G9" s="7" t="n">
-        <f aca="false">AVERAGE(B8:B14)</f>
-        <v>78</v>
+        <f aca="false">AVERAGE(B2:B9)</f>
+        <v>77.0125</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>5</v>
@@ -1765,8 +2180,8 @@
         <v>46072</v>
       </c>
       <c r="G10" s="7" t="n">
-        <f aca="false">AVERAGE(B9:B15)</f>
-        <v>78.1714285714286</v>
+        <f aca="false">AVERAGE(B3:B10)</f>
+        <v>76.9875</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>5</v>
@@ -1776,7 +2191,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>49.4</v>
+        <v>48.2999999999999</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1803,8 +2218,8 @@
         <v>46073</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">AVERAGE(B10:B16)</f>
-        <v>78.3428571428571</v>
+        <f aca="false">AVERAGE(B4:B11)</f>
+        <v>77.05</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>5</v>
@@ -1834,8 +2249,8 @@
         <v>46074</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">AVERAGE(B11:B17)</f>
-        <v>78.1428571428571</v>
+        <f aca="false">AVERAGE(B5:B12)</f>
+        <v>77.2125</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>5</v>
@@ -1865,8 +2280,8 @@
         <v>46075</v>
       </c>
       <c r="G13" s="7" t="n">
-        <f aca="false">AVERAGE(B12:B18)</f>
-        <v>77.8857142857143</v>
+        <f aca="false">AVERAGE(B6:B13)</f>
+        <v>77.55</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1893,8 +2308,8 @@
         <v>46076</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">AVERAGE(B13:B19)</f>
-        <v>77.6</v>
+        <f aca="false">AVERAGE(B7:B14)</f>
+        <v>77.8125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1921,8 +2336,8 @@
         <v>46077</v>
       </c>
       <c r="G15" s="7" t="n">
-        <f aca="false">AVERAGE(B14:B20)</f>
-        <v>77.3428571428571</v>
+        <f aca="false">AVERAGE(B8:B15)</f>
+        <v>77.9625</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1949,8 +2364,8 @@
         <v>46078</v>
       </c>
       <c r="G16" s="7" t="n">
-        <f aca="false">AVERAGE(B15:B21)</f>
-        <v>77.1142857142857</v>
+        <f aca="false">AVERAGE(B9:B16)</f>
+        <v>78.0875</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1977,8 +2392,8 @@
         <v>46079</v>
       </c>
       <c r="G17" s="7" t="n">
-        <f aca="false">AVERAGE(B16:B22)</f>
-        <v>77.1857142857143</v>
+        <f aca="false">AVERAGE(B10:B17)</f>
+        <v>78.1875</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2005,8 +2420,8 @@
         <v>46080</v>
       </c>
       <c r="G18" s="7" t="n">
-        <f aca="false">AVERAGE(B17:B23)</f>
-        <v>77.2285714285714</v>
+        <f aca="false">AVERAGE(B11:B18)</f>
+        <v>77.9375</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2033,8 +2448,8 @@
         <v>46081</v>
       </c>
       <c r="G19" s="7" t="n">
-        <f aca="false">AVERAGE(B18:B24)</f>
-        <v>77.1285714285714</v>
+        <f aca="false">AVERAGE(B12:B19)</f>
+        <v>77.7</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>8</v>
@@ -2064,8 +2479,8 @@
         <v>46082</v>
       </c>
       <c r="G20" s="7" t="n">
-        <f aca="false">AVERAGE(B19:B25)</f>
-        <v>77.0571428571429</v>
+        <f aca="false">AVERAGE(B13:B20)</f>
+        <v>77.5875</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2092,8 +2507,8 @@
         <v>46083</v>
       </c>
       <c r="G21" s="7" t="n">
-        <f aca="false">AVERAGE(B20:B26)</f>
-        <v>77.1666666666667</v>
+        <f aca="false">AVERAGE(B14:B21)</f>
+        <v>77.3125</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2120,8 +2535,8 @@
         <v>46084</v>
       </c>
       <c r="G22" s="7" t="n">
-        <f aca="false">AVERAGE(B21:B27)</f>
-        <v>77.1</v>
+        <f aca="false">AVERAGE(B15:B22)</f>
+        <v>77.25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2148,8 +2563,8 @@
         <v>46085</v>
       </c>
       <c r="G23" s="7" t="n">
-        <f aca="false">AVERAGE(B22:B28)</f>
-        <v>77.1</v>
+        <f aca="false">AVERAGE(B16:B23)</f>
+        <v>77.2625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2176,8 +2591,8 @@
         <v>46086</v>
       </c>
       <c r="G24" s="7" t="n">
-        <f aca="false">AVERAGE(B23:B29)</f>
-        <v>76.7333333333333</v>
+        <f aca="false">AVERAGE(B17:B24)</f>
+        <v>77.125</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2204,58 +2619,67 @@
         <v>46087</v>
       </c>
       <c r="G25" s="7" t="n">
-        <f aca="false">AVERAGE(B24:B30)</f>
-        <v>76.2</v>
+        <f aca="false">AVERAGE(B18:B25)</f>
+        <v>76.9875</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>46088</v>
       </c>
+      <c r="B26" s="1" t="n">
+        <v>75.8</v>
+      </c>
       <c r="C26" s="11" t="n">
         <f aca="false">B26-B25</f>
-        <v>-76</v>
+        <v>-0.200000000000003</v>
       </c>
       <c r="D26" s="3" t="n">
         <f aca="false">B26*2.204623</f>
-        <v>0</v>
+        <v>167.1104234</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">C26*2.204623</f>
-        <v>-167.551348</v>
+        <v>-0.440924600000006</v>
       </c>
       <c r="F26" s="4" t="n">
         <f aca="false">A26</f>
         <v>46088</v>
       </c>
       <c r="G26" s="7" t="n">
-        <f aca="false">AVERAGE(B25:B31)</f>
-        <v>76</v>
+        <f aca="false">AVERAGE(B19:B26)</f>
+        <v>76.9</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="n">
         <v>46089</v>
       </c>
+      <c r="B27" s="1" t="n">
+        <v>77</v>
+      </c>
       <c r="C27" s="11" t="n">
         <f aca="false">B27-B26</f>
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="D27" s="3" t="n">
         <f aca="false">B27*2.204623</f>
-        <v>0</v>
+        <v>169.755971</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">C27*2.204623</f>
-        <v>0</v>
+        <v>2.64554760000001</v>
       </c>
       <c r="F27" s="4" t="n">
         <f aca="false">A27</f>
         <v>46089</v>
       </c>
-      <c r="G27" s="7" t="e">
-        <f aca="false">AVERAGE(B26:B32)</f>
-        <v>#DIV/0!</v>
+      <c r="G27" s="7" t="n">
+        <f aca="false">AVERAGE(B20:B27)</f>
+        <v>76.975</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2264,7 +2688,7 @@
       </c>
       <c r="C28" s="11" t="n">
         <f aca="false">B28-B27</f>
-        <v>0</v>
+        <v>-77</v>
       </c>
       <c r="D28" s="3" t="n">
         <f aca="false">B28*2.204623</f>
@@ -2272,15 +2696,15 @@
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">C28*2.204623</f>
-        <v>0</v>
+        <v>-169.755971</v>
       </c>
       <c r="F28" s="4" t="n">
         <f aca="false">A28</f>
         <v>46090</v>
       </c>
-      <c r="G28" s="7" t="e">
-        <f aca="false">AVERAGE(B27:B33)</f>
-        <v>#DIV/0!</v>
+      <c r="G28" s="7" t="n">
+        <f aca="false">AVERAGE(B21:B28)</f>
+        <v>76.9</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2303,9 +2727,9 @@
         <f aca="false">A29</f>
         <v>46091</v>
       </c>
-      <c r="G29" s="7" t="e">
-        <f aca="false">AVERAGE(B28:B34)</f>
-        <v>#DIV/0!</v>
+      <c r="G29" s="7" t="n">
+        <f aca="false">AVERAGE(B22:B29)</f>
+        <v>76.8666666666667</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2328,9 +2752,9 @@
         <f aca="false">A30</f>
         <v>46092</v>
       </c>
-      <c r="G30" s="7" t="e">
-        <f aca="false">AVERAGE(B29:B35)</f>
-        <v>#DIV/0!</v>
+      <c r="G30" s="7" t="n">
+        <f aca="false">AVERAGE(B23:B30)</f>
+        <v>76.6</v>
       </c>
       <c r="L30" s="6"/>
     </row>
@@ -2354,9 +2778,9 @@
         <f aca="false">A31</f>
         <v>46093</v>
       </c>
-      <c r="G31" s="7" t="e">
-        <f aca="false">AVERAGE(B30:B36)</f>
-        <v>#DIV/0!</v>
+      <c r="G31" s="7" t="n">
+        <f aca="false">AVERAGE(B24:B31)</f>
+        <v>76.3</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2379,9 +2803,9 @@
         <f aca="false">A32</f>
         <v>46094</v>
       </c>
-      <c r="G32" s="7" t="e">
-        <f aca="false">AVERAGE(B31:B37)</f>
-        <v>#DIV/0!</v>
+      <c r="G32" s="7" t="n">
+        <f aca="false">AVERAGE(B25:B32)</f>
+        <v>76.2666666666667</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2404,9 +2828,9 @@
         <f aca="false">A33</f>
         <v>46095</v>
       </c>
-      <c r="G33" s="7" t="e">
-        <f aca="false">AVERAGE(B32:B38)</f>
-        <v>#DIV/0!</v>
+      <c r="G33" s="7" t="n">
+        <f aca="false">AVERAGE(B26:B33)</f>
+        <v>76.4</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2429,9 +2853,9 @@
         <f aca="false">A34</f>
         <v>46096</v>
       </c>
-      <c r="G34" s="7" t="e">
-        <f aca="false">AVERAGE(B33:B39)</f>
-        <v>#DIV/0!</v>
+      <c r="G34" s="7" t="n">
+        <f aca="false">AVERAGE(B27:B34)</f>
+        <v>77</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2455,7 +2879,7 @@
         <v>46097</v>
       </c>
       <c r="G35" s="7" t="e">
-        <f aca="false">AVERAGE(B34:B40)</f>
+        <f aca="false">AVERAGE(B28:B35)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2480,7 +2904,7 @@
         <v>46098</v>
       </c>
       <c r="G36" s="7" t="e">
-        <f aca="false">AVERAGE(B35:B41)</f>
+        <f aca="false">AVERAGE(B29:B36)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2505,7 +2929,7 @@
         <v>46099</v>
       </c>
       <c r="G37" s="7" t="e">
-        <f aca="false">AVERAGE(B36:B42)</f>
+        <f aca="false">AVERAGE(B30:B37)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -2530,7 +2954,7 @@
         <v>46100</v>
       </c>
       <c r="G38" s="7" t="e">
-        <f aca="false">AVERAGE(B37:B43)</f>
+        <f aca="false">AVERAGE(B31:B38)</f>
         <v>#DIV/0!</v>
       </c>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822510822510823"/>
-          <c:y val="0.0667532654975825"/>
-          <c:w val="0.705348415025834"/>
-          <c:h val="0.857328426066248"/>
+          <c:x val="0.0822663997392802"/>
+          <c:y val="0.0667725402439905"/>
+          <c:w val="0.705293542529913"/>
+          <c:h val="0.85699848408287"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -365,7 +365,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Monday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>Tuesday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Sunday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,25 +435,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>77.1</c:v>
+                  <c:v>76.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>78.2</c:v>
+                  <c:v>76</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77.8</c:v>
+                  <c:v>75.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>76.8</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>76.4</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>76</c:v>
-                </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>75.8</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>77</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -476,11 +476,11 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FF420E"/>
+              <a:srgbClr val="ff420e"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -490,7 +490,7 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -500,7 +500,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Monday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>Tuesday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Sunday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>77.3125</c:v>
+                  <c:v>77.125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>77.25</c:v>
+                  <c:v>76.9875</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77.2625</c:v>
+                  <c:v>76.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77.125</c:v>
+                  <c:v>76.975</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.9875</c:v>
+                  <c:v>76.8875</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.9</c:v>
+                  <c:v>76.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.975</c:v>
+                  <c:v>76.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="14905714"/>
-        <c:axId val="3933243"/>
+        <c:axId val="40149483"/>
+        <c:axId val="67795056"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="14905714"/>
+        <c:axId val="40149483"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -620,7 +620,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -629,7 +629,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3933243"/>
+        <c:crossAx val="67795056"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="3933243"/>
+        <c:axId val="67795056"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -658,7 +658,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:srgbClr val="b3b3b3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -670,7 +670,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -679,7 +679,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14905714"/>
+        <c:crossAx val="40149483"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -698,7 +698,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
+            <a:srgbClr val="b3b3b3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -727,7 +727,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -744,7 +744,7 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822083604878503"/>
-          <c:y val="0.0667725402439905"/>
-          <c:w val="0.705381249418118"/>
-          <c:h val="0.857359416732838"/>
+          <c:x val="0.0822236707328429"/>
+          <c:y val="0.0667918261246299"/>
+          <c:w val="0.705326380482354"/>
+          <c:h val="0.857029388403495"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -803,7 +803,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -903,11 +903,11 @@
           <c:order val="1"/>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="FF420E"/>
+              <a:srgbClr val="ff420e"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -917,7 +917,7 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="FF420E"/>
+                <a:srgbClr val="ff420e"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -927,7 +927,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                     <a:solidFill>
                       <a:srgbClr val="000000"/>
                     </a:solidFill>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="69284205"/>
-        <c:axId val="55093696"/>
+        <c:axId val="27934930"/>
+        <c:axId val="16251542"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69284205"/>
+        <c:axId val="27934930"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1047,7 +1047,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1056,7 +1056,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55093696"/>
+        <c:crossAx val="16251542"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55093696"/>
+        <c:axId val="16251542"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1085,7 +1085,7 @@
           <c:spPr>
             <a:ln w="0">
               <a:solidFill>
-                <a:srgbClr val="B3B3B3"/>
+                <a:srgbClr val="b3b3b3"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -1097,7 +1097,7 @@
         <c:spPr>
           <a:ln w="0">
             <a:solidFill>
-              <a:srgbClr val="B3B3B3"/>
+              <a:srgbClr val="b3b3b3"/>
             </a:solidFill>
           </a:ln>
         </c:spPr>
@@ -1106,7 +1106,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69284205"/>
+        <c:crossAx val="27934930"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1125,7 +1125,7 @@
         <a:noFill/>
         <a:ln w="0">
           <a:solidFill>
-            <a:srgbClr val="B3B3B3"/>
+            <a:srgbClr val="b3b3b3"/>
           </a:solidFill>
         </a:ln>
       </c:spPr>
@@ -1154,7 +1154,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1171,449 +1171,13 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
 </c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:lineWidthScale>1</cs:lineWidthScale>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-    <a:defRPr sz="1800" b="0"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataLabel>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <cs:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr"/>
-      </a:solidFill>
-    </cs:spPr>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointMarkerLayout>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:legend>
-  <cs:plotArea>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea>
-  <cs:plotArea3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor"/>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1627,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>680760</xdr:colOff>
+      <xdr:colOff>679320</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>176760</xdr:rowOff>
+      <xdr:rowOff>175320</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1638,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7733520" cy="4988160"/>
+        <a:ext cx="7732080" cy="4986720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1662,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>67680</xdr:colOff>
+      <xdr:colOff>66240</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>186120</xdr:rowOff>
+      <xdr:rowOff>184680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1673,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7733160" cy="4986720"/>
+        <a:ext cx="7731720" cy="4985280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1694,37 +1258,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18A303"/>
+        <a:srgbClr val="18a303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369A3"/>
+        <a:srgbClr val="0369a3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A33E03"/>
+        <a:srgbClr val="a33e03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8E03A3"/>
+        <a:srgbClr val="8e03a3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="C99C00"/>
+        <a:srgbClr val="c99c00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="C9211E"/>
+        <a:srgbClr val="c9211e"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000EE"/>
+        <a:srgbClr val="0000ee"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551A8B"/>
+        <a:srgbClr val="551a8b"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -1840,15 +1404,15 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46083</v>
+        <v>46086</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.1</v>
+        <v>76.4</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.3125</v>
+        <v>77.125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1877,15 +1441,15 @@
       <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>78.2</v>
+        <v>76</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.25</v>
+        <v>76.9875</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1914,15 +1478,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46085</v>
+        <v>46088</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.8</v>
+        <v>75.8</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.2625</v>
+        <v>76.9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1954,19 +1518,19 @@
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>77</v>
+        <v>76.4</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46086</v>
+        <v>46089</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>77</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.125</v>
+        <v>76.975</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1998,19 +1562,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>76.9</v>
+        <v>76.3142857142857</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76</v>
+        <v>76.8</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.9875</v>
+        <v>76.8875</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2040,15 +1604,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46088</v>
+        <v>46091</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.8</v>
+        <v>76.4</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.9</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2083,15 +1647,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46089</v>
+        <v>46092</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77</v>
+        <v>75.8</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.975</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2191,7 +1755,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>48.2999999999999</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2686,17 +2250,20 @@
       <c r="A28" s="5" t="n">
         <v>46090</v>
       </c>
+      <c r="B28" s="1" t="n">
+        <v>76.8</v>
+      </c>
       <c r="C28" s="11" t="n">
         <f aca="false">B28-B27</f>
-        <v>-77</v>
+        <v>-0.200000000000003</v>
       </c>
       <c r="D28" s="3" t="n">
         <f aca="false">B28*2.204623</f>
-        <v>0</v>
+        <v>169.3150464</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">C28*2.204623</f>
-        <v>-169.755971</v>
+        <v>-0.440924600000006</v>
       </c>
       <c r="F28" s="4" t="n">
         <f aca="false">A28</f>
@@ -2704,24 +2271,27 @@
       </c>
       <c r="G28" s="7" t="n">
         <f aca="false">AVERAGE(B21:B28)</f>
-        <v>76.9</v>
+        <v>76.8875</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="n">
         <v>46091</v>
       </c>
+      <c r="B29" s="1" t="n">
+        <v>76.4</v>
+      </c>
       <c r="C29" s="11" t="n">
         <f aca="false">B29-B28</f>
-        <v>0</v>
+        <v>-0.399999999999992</v>
       </c>
       <c r="D29" s="3" t="n">
         <f aca="false">B29*2.204623</f>
-        <v>0</v>
+        <v>168.4331972</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">C29*2.204623</f>
-        <v>0</v>
+        <v>-0.881849199999981</v>
       </c>
       <c r="F29" s="4" t="n">
         <f aca="false">A29</f>
@@ -2729,24 +2299,27 @@
       </c>
       <c r="G29" s="7" t="n">
         <f aca="false">AVERAGE(B22:B29)</f>
-        <v>76.8666666666667</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="n">
         <v>46092</v>
       </c>
+      <c r="B30" s="1" t="n">
+        <v>75.8</v>
+      </c>
       <c r="C30" s="11" t="n">
         <f aca="false">B30-B29</f>
-        <v>0</v>
+        <v>-0.600000000000009</v>
       </c>
       <c r="D30" s="3" t="n">
         <f aca="false">B30*2.204623</f>
-        <v>0</v>
+        <v>167.1104234</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">C30*2.204623</f>
-        <v>0</v>
+        <v>-1.32277380000002</v>
       </c>
       <c r="F30" s="4" t="n">
         <f aca="false">A30</f>
@@ -2754,7 +2327,7 @@
       </c>
       <c r="G30" s="7" t="n">
         <f aca="false">AVERAGE(B23:B30)</f>
-        <v>76.6</v>
+        <v>76.5</v>
       </c>
       <c r="L30" s="6"/>
     </row>
@@ -2764,7 +2337,7 @@
       </c>
       <c r="C31" s="11" t="n">
         <f aca="false">B31-B30</f>
-        <v>0</v>
+        <v>-75.8</v>
       </c>
       <c r="D31" s="3" t="n">
         <f aca="false">B31*2.204623</f>
@@ -2772,7 +2345,7 @@
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">C31*2.204623</f>
-        <v>0</v>
+        <v>-167.1104234</v>
       </c>
       <c r="F31" s="4" t="n">
         <f aca="false">A31</f>
@@ -2780,7 +2353,7 @@
       </c>
       <c r="G31" s="7" t="n">
         <f aca="false">AVERAGE(B24:B31)</f>
-        <v>76.3</v>
+        <v>76.3142857142857</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2805,7 +2378,7 @@
       </c>
       <c r="G32" s="7" t="n">
         <f aca="false">AVERAGE(B25:B32)</f>
-        <v>76.2666666666667</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2830,7 +2403,7 @@
       </c>
       <c r="G33" s="7" t="n">
         <f aca="false">AVERAGE(B26:B33)</f>
-        <v>76.4</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2855,7 +2428,7 @@
       </c>
       <c r="G34" s="7" t="n">
         <f aca="false">AVERAGE(B27:B34)</f>
-        <v>77</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2878,9 +2451,9 @@
         <f aca="false">A35</f>
         <v>46097</v>
       </c>
-      <c r="G35" s="7" t="e">
+      <c r="G35" s="7" t="n">
         <f aca="false">AVERAGE(B28:B35)</f>
-        <v>#DIV/0!</v>
+        <v>76.3333333333333</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2903,9 +2476,9 @@
         <f aca="false">A36</f>
         <v>46098</v>
       </c>
-      <c r="G36" s="7" t="e">
+      <c r="G36" s="7" t="n">
         <f aca="false">AVERAGE(B29:B36)</f>
-        <v>#DIV/0!</v>
+        <v>76.1</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2928,9 +2501,9 @@
         <f aca="false">A37</f>
         <v>46099</v>
       </c>
-      <c r="G37" s="7" t="e">
+      <c r="G37" s="7" t="n">
         <f aca="false">AVERAGE(B30:B37)</f>
-        <v>#DIV/0!</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822663997392802"/>
-          <c:y val="0.0667725402439905"/>
-          <c:w val="0.705293542529913"/>
-          <c:h val="0.85699848408287"/>
+          <c:x val="0.0822855546241967"/>
+          <c:y val="0.0667966493356441"/>
+          <c:w val="0.705224923162895"/>
+          <c:h val="0.856585788561525"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>Friday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>Saturday</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>Sunday</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Wednesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -438,22 +438,22 @@
                   <c:v>76.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>76</c:v>
+                  <c:v>75.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.8</c:v>
+                  <c:v>75.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>77</c:v>
+                  <c:v>75.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.8</c:v>
+                  <c:v>74.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.4</c:v>
+                  <c:v>76.9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.8</c:v>
+                  <c:v>76.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="3">
                   <c:v>Friday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="4">
                   <c:v>Saturday</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="5">
                   <c:v>Sunday</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Wednesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>77.125</c:v>
+                  <c:v>76.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>76.9875</c:v>
+                  <c:v>76.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76.9</c:v>
+                  <c:v>76.2375</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>76.975</c:v>
+                  <c:v>76.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.8875</c:v>
+                  <c:v>75.95</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.8</c:v>
+                  <c:v>76.0875</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.5</c:v>
+                  <c:v>76.025</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="40149483"/>
-        <c:axId val="67795056"/>
+        <c:axId val="76613724"/>
+        <c:axId val="53379290"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="40149483"/>
+        <c:axId val="76613724"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67795056"/>
+        <c:crossAx val="53379290"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67795056"/>
+        <c:axId val="53379290"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40149483"/>
+        <c:crossAx val="76613724"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822236707328429"/>
-          <c:y val="0.0667918261246299"/>
-          <c:w val="0.705326380482354"/>
-          <c:h val="0.857029388403495"/>
+          <c:x val="0.0822428165603316"/>
+          <c:y val="0.0668159491476452"/>
+          <c:w val="0.70525776556606"/>
+          <c:h val="0.85661658480208"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="27934930"/>
-        <c:axId val="16251542"/>
+        <c:axId val="39676877"/>
+        <c:axId val="11791042"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27934930"/>
+        <c:axId val="39676877"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16251542"/>
+        <c:crossAx val="11791042"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="16251542"/>
+        <c:axId val="11791042"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27934930"/>
+        <c:crossAx val="39676877"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1191,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>679320</xdr:colOff>
+      <xdr:colOff>677520</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>175320</xdr:rowOff>
+      <xdr:rowOff>173520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7732080" cy="4986720"/>
+        <a:ext cx="7730280" cy="4984920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1226,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>66240</xdr:colOff>
+      <xdr:colOff>64440</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>184680</xdr:rowOff>
+      <xdr:rowOff>182880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1237,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7731720" cy="4985280"/>
+        <a:ext cx="7729920" cy="4983480"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46086</v>
+        <v>46091</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>77.125</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,15 +1441,15 @@
       <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46087</v>
+        <v>46092</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76</v>
+        <v>75.8</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.9875</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,15 +1478,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46088</v>
+        <v>46093</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.8</v>
+        <v>75.7</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.9</v>
+        <v>76.2375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,19 +1518,19 @@
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>76.4</v>
+        <v>75.8</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46089</v>
+        <v>46094</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77</v>
+        <v>75.3</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.975</v>
+        <v>76.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,19 +1562,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>76.3142857142857</v>
+        <v>75.9142857142857</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46090</v>
+        <v>46095</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.8</v>
+        <v>74.8</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.8875</v>
+        <v>75.95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,15 +1604,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46091</v>
+        <v>46096</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>76.9</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.8</v>
+        <v>76.0875</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1647,15 +1647,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46092</v>
+        <v>46097</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.8</v>
+        <v>76.5</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.5</v>
+        <v>76.025</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>44.2</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,17 +2335,20 @@
       <c r="A31" s="5" t="n">
         <v>46093</v>
       </c>
+      <c r="B31" s="1" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C31" s="11" t="n">
         <f aca="false">B31-B30</f>
-        <v>-75.8</v>
+        <v>-0.0999999999999943</v>
       </c>
       <c r="D31" s="3" t="n">
         <f aca="false">B31*2.204623</f>
-        <v>0</v>
+        <v>166.8899611</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">C31*2.204623</f>
-        <v>-167.1104234</v>
+        <v>-0.220462299999987</v>
       </c>
       <c r="F31" s="4" t="n">
         <f aca="false">A31</f>
@@ -2353,24 +2356,27 @@
       </c>
       <c r="G31" s="7" t="n">
         <f aca="false">AVERAGE(B24:B31)</f>
-        <v>76.3142857142857</v>
+        <v>76.2375</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="n">
         <v>46094</v>
       </c>
+      <c r="B32" s="1" t="n">
+        <v>75.3</v>
+      </c>
       <c r="C32" s="11" t="n">
         <f aca="false">B32-B31</f>
-        <v>0</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D32" s="3" t="n">
         <f aca="false">B32*2.204623</f>
-        <v>0</v>
+        <v>166.0081119</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">C32*2.204623</f>
-        <v>0</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F32" s="4" t="n">
         <f aca="false">A32</f>
@@ -2378,24 +2384,27 @@
       </c>
       <c r="G32" s="7" t="n">
         <f aca="false">AVERAGE(B25:B32)</f>
-        <v>76.3</v>
+        <v>76.1</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="n">
         <v>46095</v>
       </c>
+      <c r="B33" s="1" t="n">
+        <v>74.8</v>
+      </c>
       <c r="C33" s="11" t="n">
         <f aca="false">B33-B32</f>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="D33" s="3" t="n">
         <f aca="false">B33*2.204623</f>
-        <v>0</v>
+        <v>164.9058004</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">C33*2.204623</f>
-        <v>0</v>
+        <v>-1.1023115</v>
       </c>
       <c r="F33" s="4" t="n">
         <f aca="false">A33</f>
@@ -2403,24 +2412,30 @@
       </c>
       <c r="G33" s="7" t="n">
         <f aca="false">AVERAGE(B26:B33)</f>
-        <v>76.36</v>
+        <v>75.95</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5" t="n">
         <v>46096</v>
       </c>
+      <c r="B34" s="1" t="n">
+        <v>76.9</v>
+      </c>
       <c r="C34" s="11" t="n">
         <f aca="false">B34-B33</f>
-        <v>0</v>
+        <v>2.10000000000001</v>
       </c>
       <c r="D34" s="3" t="n">
         <f aca="false">B34*2.204623</f>
-        <v>0</v>
+        <v>169.5355087</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">C34*2.204623</f>
-        <v>0</v>
+        <v>4.62970830000002</v>
       </c>
       <c r="F34" s="4" t="n">
         <f aca="false">A34</f>
@@ -2428,24 +2443,27 @@
       </c>
       <c r="G34" s="7" t="n">
         <f aca="false">AVERAGE(B27:B34)</f>
-        <v>76.5</v>
+        <v>76.0875</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="n">
         <v>46097</v>
       </c>
+      <c r="B35" s="1" t="n">
+        <v>76.5</v>
+      </c>
       <c r="C35" s="11" t="n">
         <f aca="false">B35-B34</f>
-        <v>0</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D35" s="3" t="n">
         <f aca="false">B35*2.204623</f>
-        <v>0</v>
+        <v>168.6536595</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">C35*2.204623</f>
-        <v>0</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F35" s="4" t="n">
         <f aca="false">A35</f>
@@ -2453,7 +2471,7 @@
       </c>
       <c r="G35" s="7" t="n">
         <f aca="false">AVERAGE(B28:B35)</f>
-        <v>76.3333333333333</v>
+        <v>76.025</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2462,7 +2480,7 @@
       </c>
       <c r="C36" s="11" t="n">
         <f aca="false">B36-B35</f>
-        <v>0</v>
+        <v>-76.5</v>
       </c>
       <c r="D36" s="3" t="n">
         <f aca="false">B36*2.204623</f>
@@ -2470,7 +2488,7 @@
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">C36*2.204623</f>
-        <v>0</v>
+        <v>-168.6536595</v>
       </c>
       <c r="F36" s="4" t="n">
         <f aca="false">A36</f>
@@ -2478,7 +2496,7 @@
       </c>
       <c r="G36" s="7" t="n">
         <f aca="false">AVERAGE(B29:B36)</f>
-        <v>76.1</v>
+        <v>75.9142857142857</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2503,7 +2521,7 @@
       </c>
       <c r="G37" s="7" t="n">
         <f aca="false">AVERAGE(B30:B37)</f>
-        <v>75.8</v>
+        <v>75.8333333333333</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2526,9 +2544,9 @@
         <f aca="false">A38</f>
         <v>46100</v>
       </c>
-      <c r="G38" s="7" t="e">
+      <c r="G38" s="7" t="n">
         <f aca="false">AVERAGE(B31:B38)</f>
-        <v>#DIV/0!</v>
+        <v>75.84</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822855546241967"/>
-          <c:y val="0.0667966493356441"/>
-          <c:w val="0.705224923162895"/>
-          <c:h val="0.856585788561525"/>
+          <c:x val="0.0823277267856311"/>
+          <c:y val="0.0668497506684975"/>
+          <c:w val="0.705073848017519"/>
+          <c:h val="0.855676808556768"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Tuesday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Monday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,25 +435,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>76.4</c:v>
+                  <c:v>75.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75.8</c:v>
+                  <c:v>75</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>75.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>75.7</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>75.3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>74.8</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.9</c:v>
+                  <c:v>75.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.5</c:v>
+                  <c:v>75.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Tuesday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="6">
                   <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Monday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>76.8</c:v>
+                  <c:v>75.7875</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>76.5</c:v>
+                  <c:v>75.7</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>76.2375</c:v>
+                  <c:v>75.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>76.1</c:v>
+                  <c:v>75.925</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.95</c:v>
+                  <c:v>75.775</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>76.0875</c:v>
+                  <c:v>75.6375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.025</c:v>
+                  <c:v>75.5375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="76613724"/>
-        <c:axId val="53379290"/>
+        <c:axId val="43445726"/>
+        <c:axId val="43739184"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="76613724"/>
+        <c:axId val="43445726"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53379290"/>
+        <c:crossAx val="43739184"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53379290"/>
+        <c:axId val="43739184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76613724"/>
+        <c:crossAx val="43445726"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822428165603316"/>
-          <c:y val="0.0668159491476452"/>
-          <c:w val="0.70525776556606"/>
-          <c:h val="0.85661658480208"/>
+          <c:x val="0.0822849687820334"/>
+          <c:y val="0.0668690811826791"/>
+          <c:w val="0.705106700214332"/>
+          <c:h val="0.855707366442565"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="39676877"/>
-        <c:axId val="11791042"/>
+        <c:axId val="969641"/>
+        <c:axId val="77054155"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="39676877"/>
+        <c:axId val="969641"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11791042"/>
+        <c:crossAx val="77054155"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11791042"/>
+        <c:axId val="77054155"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39676877"/>
+        <c:crossAx val="969641"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1191,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>677520</xdr:colOff>
+      <xdr:colOff>673560</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>173520</xdr:rowOff>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7730280" cy="4984920"/>
+        <a:ext cx="7726320" cy="4980960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1226,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>64440</xdr:colOff>
+      <xdr:colOff>60480</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>182880</xdr:rowOff>
+      <xdr:rowOff>178920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1237,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7729920" cy="4983480"/>
+        <a:ext cx="7725960" cy="4979520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1404,15 +1404,15 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46091</v>
+        <v>46100</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.4</v>
+        <v>75.5</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.8</v>
+        <v>75.7875</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,15 +1441,15 @@
       <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46092</v>
+        <v>46101</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.8</v>
+        <v>75</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.5</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,15 +1478,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46093</v>
+        <v>46102</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.7</v>
+        <v>75.3</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.2375</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,19 +1518,19 @@
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.8</v>
+        <v>75.3</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46094</v>
+        <v>46103</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.3</v>
+        <v>76.6</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.1</v>
+        <v>75.925</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,19 +1562,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.9142857142857</v>
+        <v>75.4857142857143</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46095</v>
+        <v>46104</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>74.8</v>
+        <v>75.7</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.95</v>
+        <v>75.775</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,15 +1604,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46096</v>
+        <v>46105</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.9</v>
+        <v>75.2</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.0875</v>
+        <v>75.6375</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1647,15 +1647,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46097</v>
+        <v>46106</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.5</v>
+        <v>75.1</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>76.025</v>
+        <v>75.5375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>41.4</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2451,19 +2451,19 @@
         <v>46097</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>76.5</v>
+        <v>76.3</v>
       </c>
       <c r="C35" s="11" t="n">
         <f aca="false">B35-B34</f>
-        <v>-0.400000000000006</v>
+        <v>-0.600000000000009</v>
       </c>
       <c r="D35" s="3" t="n">
         <f aca="false">B35*2.204623</f>
-        <v>168.6536595</v>
+        <v>168.2127349</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">C35*2.204623</f>
-        <v>-0.881849200000013</v>
+        <v>-1.32277380000002</v>
       </c>
       <c r="F35" s="4" t="n">
         <f aca="false">A35</f>
@@ -2471,24 +2471,27 @@
       </c>
       <c r="G35" s="7" t="n">
         <f aca="false">AVERAGE(B28:B35)</f>
-        <v>76.025</v>
+        <v>76</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="n">
         <v>46098</v>
       </c>
+      <c r="B36" s="1" t="n">
+        <v>75.9</v>
+      </c>
       <c r="C36" s="11" t="n">
         <f aca="false">B36-B35</f>
-        <v>-76.5</v>
+        <v>-0.399999999999992</v>
       </c>
       <c r="D36" s="3" t="n">
         <f aca="false">B36*2.204623</f>
-        <v>0</v>
+        <v>167.3308857</v>
       </c>
       <c r="E36" s="7" t="n">
         <f aca="false">C36*2.204623</f>
-        <v>-168.6536595</v>
+        <v>-0.881849199999981</v>
       </c>
       <c r="F36" s="4" t="n">
         <f aca="false">A36</f>
@@ -2496,20 +2499,23 @@
       </c>
       <c r="G36" s="7" t="n">
         <f aca="false">AVERAGE(B29:B36)</f>
-        <v>75.9142857142857</v>
+        <v>75.8875</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5" t="n">
         <v>46099</v>
       </c>
+      <c r="B37" s="1" t="n">
+        <v>75.9</v>
+      </c>
       <c r="C37" s="11" t="n">
         <f aca="false">B37-B36</f>
         <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
         <f aca="false">B37*2.204623</f>
-        <v>0</v>
+        <v>167.3308857</v>
       </c>
       <c r="E37" s="7" t="n">
         <f aca="false">C37*2.204623</f>
@@ -2521,24 +2527,27 @@
       </c>
       <c r="G37" s="7" t="n">
         <f aca="false">AVERAGE(B30:B37)</f>
-        <v>75.8333333333333</v>
+        <v>75.825</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="n">
         <v>46100</v>
       </c>
+      <c r="B38" s="1" t="n">
+        <v>75.5</v>
+      </c>
       <c r="C38" s="11" t="n">
         <f aca="false">B38-B37</f>
-        <v>0</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D38" s="3" t="n">
         <f aca="false">B38*2.204623</f>
-        <v>0</v>
+        <v>166.4490365</v>
       </c>
       <c r="E38" s="7" t="n">
         <f aca="false">C38*2.204623</f>
-        <v>0</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F38" s="4" t="n">
         <f aca="false">A38</f>
@@ -2546,92 +2555,329 @@
       </c>
       <c r="G38" s="7" t="n">
         <f aca="false">AVERAGE(B31:B38)</f>
-        <v>75.84</v>
+        <v>75.7875</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="C39" s="11"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="7"/>
+      <c r="A39" s="5" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <f aca="false">B39-B38</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <f aca="false">B39*2.204623</f>
+        <v>165.346725</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <f aca="false">C39*2.204623</f>
+        <v>-1.1023115</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <f aca="false">A39</f>
+        <v>46101</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <f aca="false">AVERAGE(B32:B39)</f>
+        <v>75.7</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="C40" s="11"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="7"/>
+      <c r="A40" s="5" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <f aca="false">B40-B39</f>
+        <v>0.299999999999997</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <f aca="false">B40*2.204623</f>
+        <v>166.0081119</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <f aca="false">C40*2.204623</f>
+        <v>0.661386899999994</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <f aca="false">A40</f>
+        <v>46102</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <f aca="false">AVERAGE(B33:B40)</f>
+        <v>75.7</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="C41" s="11"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="7"/>
+      <c r="A41" s="5" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>76.6</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <f aca="false">B41-B40</f>
+        <v>1.3</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <f aca="false">B41*2.204623</f>
+        <v>168.8741218</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <f aca="false">C41*2.204623</f>
+        <v>2.86600989999999</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <f aca="false">A41</f>
+        <v>46103</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <f aca="false">AVERAGE(B34:B41)</f>
+        <v>75.925</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="C42" s="11"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="7"/>
+      <c r="A42" s="5" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <f aca="false">B42-B41</f>
+        <v>-0.899999999999992</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <f aca="false">B42*2.204623</f>
+        <v>166.8899611</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <f aca="false">C42*2.204623</f>
+        <v>-1.98416069999998</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <f aca="false">A42</f>
+        <v>46104</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <f aca="false">AVERAGE(B35:B42)</f>
+        <v>75.775</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="C43" s="11"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="7"/>
+      <c r="A43" s="5" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <f aca="false">B43-B42</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <f aca="false">B43*2.204623</f>
+        <v>165.7876496</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <f aca="false">C43*2.204623</f>
+        <v>-1.1023115</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <f aca="false">A43</f>
+        <v>46105</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <f aca="false">AVERAGE(B36:B43)</f>
+        <v>75.6375</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="C44" s="11"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="7"/>
+      <c r="A44" s="5" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <f aca="false">B44-B43</f>
+        <v>-0.100000000000009</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <f aca="false">B44*2.204623</f>
+        <v>165.5671873</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <f aca="false">C44*2.204623</f>
+        <v>-0.220462300000019</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <f aca="false">A44</f>
+        <v>46106</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <f aca="false">AVERAGE(B37:B44)</f>
+        <v>75.5375</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="C45" s="11"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="7"/>
+      <c r="A45" s="5" t="n">
+        <v>46107</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <f aca="false">B45-B44</f>
+        <v>-75.1</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <f aca="false">B45*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <f aca="false">C45*2.204623</f>
+        <v>-165.5671873</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <f aca="false">A45</f>
+        <v>46107</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <f aca="false">AVERAGE(B38:B45)</f>
+        <v>75.4857142857143</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
-      <c r="C46" s="11"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="7"/>
+      <c r="A46" s="5" t="n">
+        <v>46108</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <f aca="false">B46-B45</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <f aca="false">B46*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <f aca="false">C46*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <f aca="false">A46</f>
+        <v>46108</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <f aca="false">AVERAGE(B39:B46)</f>
+        <v>75.4833333333333</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
-      <c r="C47" s="11"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="7"/>
+      <c r="A47" s="5" t="n">
+        <v>46109</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <f aca="false">B47-B46</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <f aca="false">B47*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <f aca="false">C47*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <f aca="false">A47</f>
+        <v>46109</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <f aca="false">AVERAGE(B40:B47)</f>
+        <v>75.58</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="C48" s="11"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="7"/>
+      <c r="A48" s="5" t="n">
+        <v>46110</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <f aca="false">B48-B47</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <f aca="false">B48*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <f aca="false">C48*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <f aca="false">A48</f>
+        <v>46110</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <f aca="false">AVERAGE(B41:B48)</f>
+        <v>75.65</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5"/>
-      <c r="C49" s="11"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="7"/>
+      <c r="A49" s="5" t="n">
+        <v>46111</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <f aca="false">B49-B48</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <f aca="false">B49*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <f aca="false">C49*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <f aca="false">A49</f>
+        <v>46111</v>
+      </c>
+      <c r="G49" s="7" t="n">
+        <f aca="false">AVERAGE(B42:B49)</f>
+        <v>75.3333333333333</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5"/>
-      <c r="C50" s="11"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="7"/>
+      <c r="A50" s="5" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <f aca="false">B50-B49</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <f aca="false">B50*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <f aca="false">C50*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <f aca="false">A50</f>
+        <v>46112</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <f aca="false">AVERAGE(B43:B50)</f>
+        <v>75.15</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0823277267856311"/>
-          <c:y val="0.0668497506684975"/>
-          <c:w val="0.705073848017519"/>
-          <c:h val="0.855676808556768"/>
+          <c:x val="0.0823469102432659"/>
+          <c:y val="0.0668739155581261"/>
+          <c:w val="0.705005126293224"/>
+          <c:h val="0.855263157894737"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -405,25 +405,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Friday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Saturday</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Sunday</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Monday</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Wednesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -435,25 +435,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>75.5</c:v>
+                  <c:v>75.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75</c:v>
+                  <c:v>74.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.3</c:v>
+                  <c:v>74.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>74.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>76.6</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>75.7</c:v>
-                </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.2</c:v>
+                  <c:v>75.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.1</c:v>
+                  <c:v>74.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -540,25 +540,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>Friday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>Saturday</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Sunday</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>Monday</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>Tuesday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Wednesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>75.7875</c:v>
+                  <c:v>75.5375</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75.7</c:v>
+                  <c:v>75.375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.7</c:v>
+                  <c:v>75.2625</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>75.925</c:v>
+                  <c:v>75.2375</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.775</c:v>
+                  <c:v>75.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.6375</c:v>
+                  <c:v>75.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.5375</c:v>
+                  <c:v>75.1875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="43445726"/>
-        <c:axId val="43739184"/>
+        <c:axId val="55257847"/>
+        <c:axId val="19700501"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="43445726"/>
+        <c:axId val="55257847"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43739184"/>
+        <c:crossAx val="19700501"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43739184"/>
+        <c:axId val="19700501"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43445726"/>
+        <c:crossAx val="55257847"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0822849687820334"/>
-          <c:y val="0.0668690811826791"/>
-          <c:w val="0.705106700214332"/>
-          <c:h val="0.855707366442565"/>
+          <c:x val="0.0823041431700611"/>
+          <c:y val="0.0668932600520683"/>
+          <c:w val="0.705037982942629"/>
+          <c:h val="0.85529360717385"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="969641"/>
-        <c:axId val="77054155"/>
+        <c:axId val="91346815"/>
+        <c:axId val="73299382"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="969641"/>
+        <c:axId val="91346815"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77054155"/>
+        <c:crossAx val="73299382"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="77054155"/>
+        <c:axId val="73299382"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="969641"/>
+        <c:crossAx val="91346815"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1191,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>673560</xdr:colOff>
+      <xdr:colOff>671760</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>169560</xdr:rowOff>
+      <xdr:rowOff>167760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7726320" cy="4980960"/>
+        <a:ext cx="7724520" cy="4979160"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1226,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>60480</xdr:colOff>
+      <xdr:colOff>58680</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>178920</xdr:rowOff>
+      <xdr:rowOff>177120</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1237,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7725960" cy="4979520"/>
+        <a:ext cx="7724160" cy="4977720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1404,15 +1404,15 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46100</v>
+        <v>46106</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.5</v>
+        <v>75.1</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.7875</v>
+        <v>75.5375</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,15 +1441,15 @@
       <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46101</v>
+        <v>46107</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75</v>
+        <v>74.6</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.7</v>
+        <v>75.375</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,15 +1478,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46102</v>
+        <v>46108</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.3</v>
+        <v>74.6</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.7</v>
+        <v>75.2625</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,19 +1518,19 @@
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.3</v>
+        <v>74.8</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46103</v>
+        <v>46109</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.6</v>
+        <v>74.8</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.925</v>
+        <v>75.2375</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,19 +1562,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.4857142857143</v>
+        <v>75.1857142857143</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46104</v>
+        <v>46110</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.7</v>
+        <v>76.6</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.775</v>
+        <v>75.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,15 +1604,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46105</v>
+        <v>46111</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.2</v>
+        <v>75.8</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.6375</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1647,15 +1647,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46106</v>
+        <v>46112</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.1</v>
+        <v>74.8</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.5375</v>
+        <v>75.1875</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>38.4</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2733,17 +2733,20 @@
       <c r="A45" s="5" t="n">
         <v>46107</v>
       </c>
+      <c r="B45" s="1" t="n">
+        <v>74.6</v>
+      </c>
       <c r="C45" s="11" t="n">
         <f aca="false">B45-B44</f>
-        <v>-75.1</v>
+        <v>-0.5</v>
       </c>
       <c r="D45" s="3" t="n">
         <f aca="false">B45*2.204623</f>
-        <v>0</v>
+        <v>164.4648758</v>
       </c>
       <c r="E45" s="7" t="n">
         <f aca="false">C45*2.204623</f>
-        <v>-165.5671873</v>
+        <v>-1.1023115</v>
       </c>
       <c r="F45" s="4" t="n">
         <f aca="false">A45</f>
@@ -2751,20 +2754,23 @@
       </c>
       <c r="G45" s="7" t="n">
         <f aca="false">AVERAGE(B38:B45)</f>
-        <v>75.4857142857143</v>
+        <v>75.375</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="n">
         <v>46108</v>
       </c>
+      <c r="B46" s="1" t="n">
+        <v>74.6</v>
+      </c>
       <c r="C46" s="11" t="n">
         <f aca="false">B46-B45</f>
         <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
         <f aca="false">B46*2.204623</f>
-        <v>0</v>
+        <v>164.4648758</v>
       </c>
       <c r="E46" s="7" t="n">
         <f aca="false">C46*2.204623</f>
@@ -2776,24 +2782,27 @@
       </c>
       <c r="G46" s="7" t="n">
         <f aca="false">AVERAGE(B39:B46)</f>
-        <v>75.4833333333333</v>
+        <v>75.2625</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="n">
         <v>46109</v>
       </c>
+      <c r="B47" s="1" t="n">
+        <v>74.8</v>
+      </c>
       <c r="C47" s="11" t="n">
         <f aca="false">B47-B46</f>
-        <v>0</v>
+        <v>0.200000000000003</v>
       </c>
       <c r="D47" s="3" t="n">
         <f aca="false">B47*2.204623</f>
-        <v>0</v>
+        <v>164.9058004</v>
       </c>
       <c r="E47" s="7" t="n">
         <f aca="false">C47*2.204623</f>
-        <v>0</v>
+        <v>0.440924600000006</v>
       </c>
       <c r="F47" s="4" t="n">
         <f aca="false">A47</f>
@@ -2801,24 +2810,30 @@
       </c>
       <c r="G47" s="7" t="n">
         <f aca="false">AVERAGE(B40:B47)</f>
-        <v>75.58</v>
+        <v>75.2375</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="n">
         <v>46110</v>
       </c>
+      <c r="B48" s="1" t="n">
+        <v>76.6</v>
+      </c>
       <c r="C48" s="11" t="n">
         <f aca="false">B48-B47</f>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D48" s="3" t="n">
         <f aca="false">B48*2.204623</f>
-        <v>0</v>
+        <v>168.8741218</v>
       </c>
       <c r="E48" s="7" t="n">
         <f aca="false">C48*2.204623</f>
-        <v>0</v>
+        <v>3.96832139999999</v>
       </c>
       <c r="F48" s="4" t="n">
         <f aca="false">A48</f>
@@ -2826,24 +2841,27 @@
       </c>
       <c r="G48" s="7" t="n">
         <f aca="false">AVERAGE(B41:B48)</f>
-        <v>75.65</v>
+        <v>75.4</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="n">
         <v>46111</v>
       </c>
+      <c r="B49" s="1" t="n">
+        <v>75.8</v>
+      </c>
       <c r="C49" s="11" t="n">
         <f aca="false">B49-B48</f>
-        <v>0</v>
+        <v>-0.799999999999997</v>
       </c>
       <c r="D49" s="3" t="n">
         <f aca="false">B49*2.204623</f>
-        <v>0</v>
+        <v>167.1104234</v>
       </c>
       <c r="E49" s="7" t="n">
         <f aca="false">C49*2.204623</f>
-        <v>0</v>
+        <v>-1.76369839999999</v>
       </c>
       <c r="F49" s="4" t="n">
         <f aca="false">A49</f>
@@ -2851,24 +2869,27 @@
       </c>
       <c r="G49" s="7" t="n">
         <f aca="false">AVERAGE(B42:B49)</f>
-        <v>75.3333333333333</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="n">
         <v>46112</v>
       </c>
+      <c r="B50" s="1" t="n">
+        <v>74.8</v>
+      </c>
       <c r="C50" s="11" t="n">
         <f aca="false">B50-B49</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D50" s="3" t="n">
         <f aca="false">B50*2.204623</f>
-        <v>0</v>
+        <v>164.9058004</v>
       </c>
       <c r="E50" s="7" t="n">
         <f aca="false">C50*2.204623</f>
-        <v>0</v>
+        <v>-2.204623</v>
       </c>
       <c r="F50" s="4" t="n">
         <f aca="false">A50</f>
@@ -2876,7 +2897,7 @@
       </c>
       <c r="G50" s="7" t="n">
         <f aca="false">AVERAGE(B43:B50)</f>
-        <v>75.15</v>
+        <v>75.1875</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
@@ -316,10 +316,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0823469102432659"/>
-          <c:y val="0.0668739155581261"/>
-          <c:w val="0.705005126293224"/>
-          <c:h val="0.855263157894737"/>
+          <c:x val="0.0823853039910481"/>
+          <c:y val="0.066922297786138"/>
+          <c:w val="0.704867586721373"/>
+          <c:h val="0.854434958761395"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -438,22 +438,22 @@
                   <c:v>75.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>74.6</c:v>
+                  <c:v>75.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>74.6</c:v>
+                  <c:v>75.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>74.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.6</c:v>
+                  <c:v>76.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.8</c:v>
+                  <c:v>75.2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>74.8</c:v>
+                  <c:v>74.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -570,25 +570,25 @@
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>75.5375</c:v>
+                  <c:v>75.6125</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>75.375</c:v>
+                  <c:v>75.5125</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.2625</c:v>
+                  <c:v>75.45</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>75.2375</c:v>
+                  <c:v>75.3875</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.4</c:v>
+                  <c:v>75.525</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.3</c:v>
+                  <c:v>75.4125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.1875</c:v>
+                  <c:v>75.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +603,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="55257847"/>
-        <c:axId val="19700501"/>
+        <c:axId val="9958738"/>
+        <c:axId val="70960367"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="55257847"/>
+        <c:axId val="9958738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -640,7 +640,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="19700501"/>
+        <c:crossAx val="70960367"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +648,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="19700501"/>
+        <c:axId val="70960367"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -690,7 +690,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55257847"/>
+        <c:crossAx val="9958738"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -765,10 +765,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0823041431700611"/>
-          <c:y val="0.0668932600520683"/>
-          <c:w val="0.705037982942629"/>
-          <c:h val="0.85529360717385"/>
+          <c:x val="0.0823425187671936"/>
+          <c:y val="0.0669416702851353"/>
+          <c:w val="0.704900452277708"/>
+          <c:h val="0.854465190331452"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1030,11 +1030,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="91346815"/>
-        <c:axId val="73299382"/>
+        <c:axId val="620345"/>
+        <c:axId val="49839955"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="91346815"/>
+        <c:axId val="620345"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1067,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73299382"/>
+        <c:crossAx val="49839955"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1075,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73299382"/>
+        <c:axId val="49839955"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1117,7 +1117,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="91346815"/>
+        <c:crossAx val="620345"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1191,9 +1191,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>671760</xdr:colOff>
+      <xdr:colOff>668160</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>167760</xdr:rowOff>
+      <xdr:rowOff>164160</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1202,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7724520" cy="4979160"/>
+        <a:ext cx="7720920" cy="4975560"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1226,9 +1226,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>58680</xdr:colOff>
+      <xdr:colOff>55080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>177120</xdr:rowOff>
+      <xdr:rowOff>173520</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1237,7 +1237,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7724160" cy="4977720"/>
+        <a:ext cx="7720560" cy="4974120"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46106</v>
+        <v>46127</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.5375</v>
+        <v>75.6125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,15 +1441,15 @@
       <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46107</v>
+        <v>46128</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>74.6</v>
+        <v>75.1</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.375</v>
+        <v>75.5125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,15 +1478,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46108</v>
+        <v>46129</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>74.6</v>
+        <v>75.1</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.2625</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1518,11 +1518,11 @@
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>74.8</v>
+        <v>75.1</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46109</v>
+        <v>46130</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.2375</v>
+        <v>75.3875</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,19 +1562,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.1857142857143</v>
+        <v>75.1142857142857</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46110</v>
+        <v>46131</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.6</v>
+        <v>76.1</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.4</v>
+        <v>75.525</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,15 +1604,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46111</v>
+        <v>46132</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.8</v>
+        <v>75.2</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.3</v>
+        <v>75.4125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1647,15 +1647,15 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46112</v>
+        <v>46133</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>74.8</v>
+        <v>74.4</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.1875</v>
+        <v>75.15</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>36.3</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2901,214 +2901,828 @@
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5"/>
-      <c r="C51" s="11"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="7"/>
+      <c r="A51" s="5" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>74.1</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <f aca="false">B51-B50</f>
+        <v>-0.700000000000003</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <f aca="false">B51*2.204623</f>
+        <v>163.3625643</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <f aca="false">C51*2.204623</f>
+        <v>-1.54323610000001</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <f aca="false">A51</f>
+        <v>46113</v>
+      </c>
+      <c r="G51" s="7" t="n">
+        <f aca="false">AVERAGE(B44:B51)</f>
+        <v>75.05</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5"/>
-      <c r="C52" s="11"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="7"/>
+      <c r="A52" s="5" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>73.6</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <f aca="false">B52-B51</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <f aca="false">B52*2.204623</f>
+        <v>162.2602528</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <f aca="false">C52*2.204623</f>
+        <v>-1.1023115</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <f aca="false">A52</f>
+        <v>46114</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <f aca="false">AVERAGE(B45:B52)</f>
+        <v>74.8625</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5"/>
-      <c r="C53" s="11"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="7"/>
+      <c r="A53" s="5" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <f aca="false">B53-B52</f>
+        <v>1.40000000000001</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <f aca="false">B53*2.204623</f>
+        <v>165.346725</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <f aca="false">C53*2.204623</f>
+        <v>3.08647220000001</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <f aca="false">A53</f>
+        <v>46115</v>
+      </c>
+      <c r="G53" s="7" t="n">
+        <f aca="false">AVERAGE(B46:B53)</f>
+        <v>74.9125</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5"/>
-      <c r="C54" s="11"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="7"/>
+      <c r="A54" s="5" t="n">
+        <v>46116</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <f aca="false">B54-B53</f>
+        <v>0.5</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <f aca="false">B54*2.204623</f>
+        <v>166.4490365</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <f aca="false">C54*2.204623</f>
+        <v>1.1023115</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <f aca="false">A54</f>
+        <v>46116</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <f aca="false">AVERAGE(B47:B54)</f>
+        <v>75.025</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
-      <c r="C55" s="11"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="7"/>
+      <c r="A55" s="5" t="n">
+        <v>46117</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>75.6</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <f aca="false">B55-B54</f>
+        <v>0.0999999999999943</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <f aca="false">B55*2.204623</f>
+        <v>166.6694988</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <f aca="false">C55*2.204623</f>
+        <v>0.220462299999987</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <f aca="false">A55</f>
+        <v>46117</v>
+      </c>
+      <c r="G55" s="7" t="n">
+        <f aca="false">AVERAGE(B48:B55)</f>
+        <v>75.125</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="C56" s="11"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="7"/>
+      <c r="A56" s="5" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <f aca="false">B56-B55</f>
+        <v>0.400000000000006</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <f aca="false">B56*2.204623</f>
+        <v>167.551348</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <f aca="false">C56*2.204623</f>
+        <v>0.881849200000013</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <f aca="false">A56</f>
+        <v>46118</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <f aca="false">AVERAGE(B49:B56)</f>
+        <v>75.05</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5"/>
-      <c r="C57" s="11"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="7"/>
+      <c r="A57" s="5" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <f aca="false">B57-B56</f>
+        <v>0.700000000000003</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <f aca="false">B57*2.204623</f>
+        <v>169.0945841</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <f aca="false">C57*2.204623</f>
+        <v>1.54323610000001</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <f aca="false">A57</f>
+        <v>46119</v>
+      </c>
+      <c r="G57" s="7" t="n">
+        <f aca="false">AVERAGE(B50:B57)</f>
+        <v>75.1625</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="11"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="7"/>
+      <c r="A58" s="5" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>75.9</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <f aca="false">B58-B57</f>
+        <v>-0.799999999999997</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <f aca="false">B58*2.204623</f>
+        <v>167.3308857</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <f aca="false">C58*2.204623</f>
+        <v>-1.76369839999999</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <f aca="false">A58</f>
+        <v>46120</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <f aca="false">AVERAGE(B51:B58)</f>
+        <v>75.3</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5"/>
-      <c r="C59" s="11"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="7"/>
+      <c r="A59" s="5" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>75.6</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <f aca="false">B59-B58</f>
+        <v>-0.300000000000011</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <f aca="false">B59*2.204623</f>
+        <v>166.6694988</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <f aca="false">C59*2.204623</f>
+        <v>-0.661386900000025</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <f aca="false">A59</f>
+        <v>46121</v>
+      </c>
+      <c r="G59" s="7" t="n">
+        <f aca="false">AVERAGE(B52:B59)</f>
+        <v>75.4875</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5"/>
-      <c r="C60" s="11"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="7"/>
+      <c r="A60" s="5" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <f aca="false">B60-B59</f>
+        <v>-0.299999999999997</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <f aca="false">B60*2.204623</f>
+        <v>166.0081119</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <f aca="false">C60*2.204623</f>
+        <v>-0.661386899999994</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <f aca="false">A60</f>
+        <v>46122</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <f aca="false">AVERAGE(B53:B60)</f>
+        <v>75.7</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5"/>
-      <c r="C61" s="11"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="7"/>
+      <c r="A61" s="5" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <f aca="false">B61-B60</f>
+        <v>-0.299999999999997</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <f aca="false">B61*2.204623</f>
+        <v>165.346725</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <f aca="false">C61*2.204623</f>
+        <v>-0.661386899999994</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <f aca="false">A61</f>
+        <v>46123</v>
+      </c>
+      <c r="G61" s="7" t="n">
+        <f aca="false">AVERAGE(B54:B61)</f>
+        <v>75.7</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5"/>
-      <c r="C62" s="11"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="7"/>
+      <c r="A62" s="5" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <f aca="false">B62-B61</f>
+        <v>1.09999999999999</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <f aca="false">B62*2.204623</f>
+        <v>167.7718103</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <f aca="false">C62*2.204623</f>
+        <v>2.42508529999999</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <f aca="false">A62</f>
+        <v>46124</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <f aca="false">AVERAGE(B55:B62)</f>
+        <v>75.775</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5"/>
-      <c r="C63" s="11"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="7"/>
+      <c r="A63" s="5" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <f aca="false">B63-B62</f>
+        <v>0.400000000000006</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <f aca="false">B63*2.204623</f>
+        <v>168.6536595</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <f aca="false">C63*2.204623</f>
+        <v>0.881849200000013</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <f aca="false">A63</f>
+        <v>46125</v>
+      </c>
+      <c r="G63" s="7" t="n">
+        <f aca="false">AVERAGE(B56:B63)</f>
+        <v>75.8875</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5"/>
-      <c r="C64" s="11"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="7"/>
+      <c r="A64" s="5" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>75.4</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <f aca="false">B64-B63</f>
+        <v>-1.09999999999999</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <f aca="false">B64*2.204623</f>
+        <v>166.2285742</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <f aca="false">C64*2.204623</f>
+        <v>-2.42508529999999</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <f aca="false">A64</f>
+        <v>46126</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <f aca="false">AVERAGE(B57:B64)</f>
+        <v>75.8125</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5"/>
-      <c r="C65" s="11"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="7"/>
+      <c r="A65" s="5" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <f aca="false">B65-B64</f>
+        <v>-0.300000000000011</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <f aca="false">B65*2.204623</f>
+        <v>165.5671873</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <f aca="false">C65*2.204623</f>
+        <v>-0.661386900000025</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <f aca="false">A65</f>
+        <v>46127</v>
+      </c>
+      <c r="G65" s="7" t="n">
+        <f aca="false">AVERAGE(B58:B65)</f>
+        <v>75.6125</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5"/>
-      <c r="C66" s="11"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="7"/>
+      <c r="A66" s="5" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <f aca="false">B66-B65</f>
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <f aca="false">B66*2.204623</f>
+        <v>165.5671873</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <f aca="false">C66*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <f aca="false">A66</f>
+        <v>46128</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <f aca="false">AVERAGE(B59:B66)</f>
+        <v>75.5125</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5"/>
-      <c r="C67" s="11"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="7"/>
+      <c r="A67" s="5" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>75.1</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <f aca="false">B67-B66</f>
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <f aca="false">B67*2.204623</f>
+        <v>165.5671873</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <f aca="false">C67*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <f aca="false">A67</f>
+        <v>46129</v>
+      </c>
+      <c r="G67" s="7" t="n">
+        <f aca="false">AVERAGE(B60:B67)</f>
+        <v>75.45</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5"/>
-      <c r="C68" s="11"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="7"/>
+      <c r="A68" s="5" t="n">
+        <v>46130</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <f aca="false">B68-B67</f>
+        <v>-0.299999999999997</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <f aca="false">B68*2.204623</f>
+        <v>164.9058004</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <f aca="false">C68*2.204623</f>
+        <v>-0.661386899999994</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <f aca="false">A68</f>
+        <v>46130</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <f aca="false">AVERAGE(B61:B68)</f>
+        <v>75.3875</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5"/>
-      <c r="C69" s="11"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="7"/>
+      <c r="A69" s="5" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>76.1</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <f aca="false">B69-B68</f>
+        <v>1.3</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <f aca="false">B69*2.204623</f>
+        <v>167.7718103</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <f aca="false">C69*2.204623</f>
+        <v>2.86600989999999</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <f aca="false">A69</f>
+        <v>46131</v>
+      </c>
+      <c r="G69" s="7" t="n">
+        <f aca="false">AVERAGE(B62:B69)</f>
+        <v>75.525</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5"/>
-      <c r="C70" s="11"/>
-      <c r="E70" s="7"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="7"/>
+      <c r="A70" s="5" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <f aca="false">B70-B69</f>
+        <v>-0.899999999999992</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <f aca="false">B70*2.204623</f>
+        <v>165.7876496</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <f aca="false">C70*2.204623</f>
+        <v>-1.98416069999998</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <f aca="false">A70</f>
+        <v>46132</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <f aca="false">AVERAGE(B63:B70)</f>
+        <v>75.4125</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5"/>
-      <c r="C71" s="11"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="7"/>
+      <c r="A71" s="5" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>74.4</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <f aca="false">B71-B70</f>
+        <v>-0.799999999999997</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <f aca="false">B71*2.204623</f>
+        <v>164.0239512</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <f aca="false">C71*2.204623</f>
+        <v>-1.76369839999999</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <f aca="false">A71</f>
+        <v>46133</v>
+      </c>
+      <c r="G71" s="7" t="n">
+        <f aca="false">AVERAGE(B64:B71)</f>
+        <v>75.15</v>
+      </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5"/>
-      <c r="C72" s="11"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="7"/>
+      <c r="A72" s="5" t="n">
+        <v>46134</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <f aca="false">B72-B71</f>
+        <v>-74.4</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <f aca="false">B72*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <f aca="false">C72*2.204623</f>
+        <v>-164.0239512</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <f aca="false">A72</f>
+        <v>46134</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <f aca="false">AVERAGE(B65:B72)</f>
+        <v>75.1142857142857</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5"/>
-      <c r="C73" s="11"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="7"/>
+      <c r="A73" s="5" t="n">
+        <v>46135</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <f aca="false">B73-B72</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <f aca="false">B73*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <f aca="false">C73*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <f aca="false">A73</f>
+        <v>46135</v>
+      </c>
+      <c r="G73" s="7" t="n">
+        <f aca="false">AVERAGE(B66:B73)</f>
+        <v>75.1166666666667</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5"/>
-      <c r="C74" s="11"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="7"/>
+      <c r="A74" s="5" t="n">
+        <v>46136</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <f aca="false">B74-B73</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <f aca="false">B74*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <f aca="false">C74*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <f aca="false">A74</f>
+        <v>46136</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <f aca="false">AVERAGE(B67:B74)</f>
+        <v>75.12</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5"/>
+      <c r="A75" s="5" t="n">
+        <v>46137</v>
+      </c>
       <c r="B75" s="13"/>
-      <c r="C75" s="11"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="7"/>
+      <c r="C75" s="11" t="n">
+        <f aca="false">B75-B74</f>
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <f aca="false">B75*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E75" s="7" t="n">
+        <f aca="false">C75*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <f aca="false">A75</f>
+        <v>46137</v>
+      </c>
+      <c r="G75" s="7" t="n">
+        <f aca="false">AVERAGE(B68:B75)</f>
+        <v>75.125</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5"/>
-      <c r="C76" s="11"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="7"/>
+      <c r="A76" s="5" t="n">
+        <v>46138</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <f aca="false">B76-B75</f>
+        <v>0</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <f aca="false">B76*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <f aca="false">C76*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <f aca="false">A76</f>
+        <v>46138</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <f aca="false">AVERAGE(B69:B76)</f>
+        <v>75.2333333333333</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5"/>
-      <c r="C77" s="11"/>
-      <c r="E77" s="7"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="7"/>
+      <c r="A77" s="5" t="n">
+        <v>46139</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <f aca="false">B77-B76</f>
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <f aca="false">B77*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E77" s="7" t="n">
+        <f aca="false">C77*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <f aca="false">A77</f>
+        <v>46139</v>
+      </c>
+      <c r="G77" s="7" t="n">
+        <f aca="false">AVERAGE(B70:B77)</f>
+        <v>74.8</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5"/>
-      <c r="C78" s="11"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="7"/>
+      <c r="A78" s="5" t="n">
+        <v>46140</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <f aca="false">B78-B77</f>
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <f aca="false">B78*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <f aca="false">C78*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <f aca="false">A78</f>
+        <v>46140</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <f aca="false">AVERAGE(B71:B78)</f>
+        <v>74.4</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5"/>
-      <c r="C79" s="11"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="7"/>
+      <c r="A79" s="5" t="n">
+        <v>46141</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <f aca="false">B79-B78</f>
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <f aca="false">B79*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E79" s="7" t="n">
+        <f aca="false">C79*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <f aca="false">A79</f>
+        <v>46141</v>
+      </c>
+      <c r="G79" s="7" t="e">
+        <f aca="false">AVERAGE(B72:B79)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5"/>
-      <c r="C80" s="11"/>
-      <c r="E80" s="7"/>
+      <c r="A80" s="5" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <f aca="false">B80-B79</f>
+        <v>0</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <f aca="false">B80*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <f aca="false">C80*2.204623</f>
+        <v>0</v>
+      </c>
       <c r="F80" s="4"/>
       <c r="G80" s="7"/>
     </row>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -9,15 +9,19 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet1_2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1_3" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1_2" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" name="COLUMN_B" vbProcedure="false">Sheet1!$B$1:INDEX(Sheet1!$B:$B, COUNTA(Sheet1!$B:$B))</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">#REF!</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Sheet_Title" vbProcedure="false">"Sheet1"</definedName>
-    <definedName function="false" hidden="false" localSheetId="1" name="COLUMN_B" vbProcedure="false">Sheet1_2!$B$1:INDEX(Sheet1_2!$B:$B, COUNTA(Sheet1_2!$B:$B))</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="COLUMN_B" vbProcedure="false">Sheet1_3!$B$1:INDEX(Sheet1_3!$B:$B, COUNTA(Sheet1_3!$B:$B))</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">#REF!</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Sheet_Title" vbProcedure="false">"Sheet1"</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="COLUMN_B" vbProcedure="false">Sheet1_2!$B$1:INDEX(Sheet1_2!$B:$B, COUNTA(Sheet1_2!$B:$B))</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">#REF!</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Sheet_Title" vbProcedure="false">"Sheet1"</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="true" iterateDelta="0.001"/>
   <extLst>
@@ -29,15 +33,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="17">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
   <si>
-    <t xml:space="preserve">Day 2 of rfl</t>
+    <t xml:space="preserve">DAY 1</t>
   </si>
   <si>
     <t xml:space="preserve">Last 7 values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DAILY CALORIE DEFICIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">remaining rfl ~days:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 2 of rfl</t>
   </si>
   <si>
     <t xml:space="preserve">7 day median</t>
@@ -49,13 +62,19 @@
     <t xml:space="preserve">refeed</t>
   </si>
   <si>
-    <t xml:space="preserve">DAILY CALORIE DEFICIT</t>
+    <t xml:space="preserve">refeed on this day</t>
   </si>
   <si>
-    <t xml:space="preserve">remaining rfl ~days:</t>
+    <t xml:space="preserve">q</t>
   </si>
   <si>
-    <t xml:space="preserve">refeed on this day</t>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inaccurate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diet break start</t>
   </si>
   <si>
     <t xml:space="preserve">LEFT</t>
@@ -316,10 +335,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0823853039910481"/>
-          <c:y val="0.066922297786138"/>
-          <c:w val="0.704867586721373"/>
-          <c:h val="0.854434958761395"/>
+          <c:x val="0.0824237335572348"/>
+          <c:y val="0.0669707500724008"/>
+          <c:w val="0.704729918835712"/>
+          <c:h val="0.853605560382276"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -405,25 +424,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Err:502</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Err:502</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Wednesday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Tuesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -434,26 +453,20 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>75.1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>75.1</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.1</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>74.8</c:v>
+                  <c:v>80.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>76.1</c:v>
+                  <c:v>77.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.2</c:v>
+                  <c:v>77</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>74.4</c:v>
+                  <c:v>76.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -540,25 +553,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
+                  <c:v>Err:502</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Err:502</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>Wednesday</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="5">
                   <c:v>Thursday</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="6">
                   <c:v>Friday</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Saturday</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Sunday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Monday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Tuesday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -569,26 +582,17 @@
               <c:numCache>
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>75.6125</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>75.5125</c:v>
-                </c:pt>
                 <c:pt idx="2">
-                  <c:v>75.45</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>75.3875</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>75.525</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>75.4125</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>75.15</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,11 +607,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="9958738"/>
-        <c:axId val="70960367"/>
+        <c:axId val="6972484"/>
+        <c:axId val="41247786"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="9958738"/>
+        <c:axId val="6972484"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -640,7 +644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70960367"/>
+        <c:crossAx val="41247786"/>
         <c:crossesAt val="0"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -648,7 +652,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="70960367"/>
+        <c:axId val="41247786"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -690,7 +694,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="9958738"/>
+        <c:crossAx val="6972484"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -765,10 +769,437 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0823425187671936"/>
-          <c:y val="0.0669416702851353"/>
-          <c:w val="0.704900452277708"/>
-          <c:h val="0.854465190331452"/>
+          <c:x val="0.0824237335572348"/>
+          <c:y val="0.0669707500724008"/>
+          <c:w val="0.704683272693348"/>
+          <c:h val="0.853605560382276"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="004586"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="004586"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1_3!$K$1:$K$7</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1_3!$L$1:$L$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>76</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>76.6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="ff420e"/>
+            </a:solidFill>
+            <a:ln w="28800">
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="8"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="ff420e"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="28800">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1_3!$K$1:$K$7</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Friday</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Saturday</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tuesday</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Wednesday</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Thursday</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1_3!$M$1:$M$7</c:f>
+              <c:numCache>
+                <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>75.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>75.5625</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>75.6875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75.6125</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>75.6125</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>75.7875</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>75.9875</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="1"/>
+        <c:axId val="70112705"/>
+        <c:axId val="73294654"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="70112705"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="dddd" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="73294654"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="73294654"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="70112705"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:solidFill>
+            <a:srgbClr val="b3b3b3"/>
+          </a:solidFill>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.803106633081444"/>
+          <c:y val="0.303069794381697"/>
+          <c:w val="0.188459206045622"/>
+          <c:h val="0.0843530519151401"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:uFillTx/>
+              <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="ffffff"/>
+    </a:solidFill>
+    <a:ln w="0">
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.0823809301674675"/>
+          <c:y val="0.0669901506373117"/>
+          <c:w val="0.704762793301302"/>
+          <c:h val="0.853635573580533"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1030,11 +1461,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="620345"/>
-        <c:axId val="49839955"/>
+        <c:axId val="99048173"/>
+        <c:axId val="10742689"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="620345"/>
+        <c:axId val="99048173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1067,7 +1498,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49839955"/>
+        <c:crossAx val="10742689"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1075,7 +1506,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49839955"/>
+        <c:axId val="10742689"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1117,7 +1548,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="620345"/>
+        <c:crossAx val="99048173"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1136,10 +1567,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.803180359882829"/>
-          <c:y val="0.303126350669932"/>
-          <c:w val="0.188459034687994"/>
-          <c:h val="0.0843599164325337"/>
+          <c:x val="0.803144096655316"/>
+          <c:y val="0.30308516801854"/>
+          <c:w val="0.188421347266281"/>
+          <c:h val="0.0843050626493807"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1191,9 +1622,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>668160</xdr:colOff>
+      <xdr:colOff>664560</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>164160</xdr:rowOff>
+      <xdr:rowOff>160560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1202,7 +1633,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7720920" cy="4975560"/>
+        <a:ext cx="7717320" cy="4971960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1219,6 +1650,41 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>394560</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>141840</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>664560</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>160560</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="11475360" y="2618280"/>
+        <a:ext cx="7717320" cy="4971960"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>712800</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -1226,18 +1692,18 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>55080</xdr:colOff>
+      <xdr:colOff>51480</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>173520</xdr:rowOff>
+      <xdr:rowOff>169920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvPr id="3" name=""/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7720560" cy="4974120"/>
+        <a:ext cx="7716960" cy="4970520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1361,7 +1827,1737 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M111"/>
+  <sheetFormatPr defaultColWidth="69.328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="3" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="21.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="4" width="13.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="256" min="12" style="1" width="13.21"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B1" s="6" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <f aca="false">B1*2.204623</f>
+        <v>177.0312269</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="4" t="n">
+        <f aca="false">A1</f>
+        <v>46175</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="8" t="e">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L1" s="9" t="e">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M1" s="10" t="e">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="C2" s="11" t="n">
+        <f aca="false">B2-B1</f>
+        <v>-2.8</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <f aca="false">B2*2.204623</f>
+        <v>170.8582825</v>
+      </c>
+      <c r="E2" s="7" t="n">
+        <f aca="false">C2*2.204623</f>
+        <v>-6.17294439999999</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <f aca="false">A2</f>
+        <v>46176</v>
+      </c>
+      <c r="G2" s="7"/>
+      <c r="K2" s="8" t="e">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="L2" s="9" t="e">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M2" s="10" t="e">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="C3" s="11" t="n">
+        <f aca="false">B3-B2</f>
+        <v>-0.5</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <f aca="false">B3*2.204623</f>
+        <v>169.755971</v>
+      </c>
+      <c r="E3" s="7" t="n">
+        <f aca="false">C3*2.204623</f>
+        <v>-1.1023115</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <f aca="false">A3</f>
+        <v>46177</v>
+      </c>
+      <c r="G3" s="7"/>
+      <c r="K3" s="8" t="n">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>46177</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>77</v>
+      </c>
+      <c r="M3" s="10" t="n">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>76.6</v>
+      </c>
+      <c r="C4" s="11" t="n">
+        <f aca="false">B4-B3</f>
+        <v>-0.400000000000006</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <f aca="false">B4*2.204623</f>
+        <v>168.8741218</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <f aca="false">C4*2.204623</f>
+        <v>-0.881849200000013</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <f aca="false">A4</f>
+        <v>46178</v>
+      </c>
+      <c r="G4" s="7"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="12" t="e">
+        <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>46175</v>
+      </c>
+      <c r="L4" s="9" t="n">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>80.3</v>
+      </c>
+      <c r="M4" s="10" t="str">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>7 day average</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="n">
+        <v>46179</v>
+      </c>
+      <c r="B5" s="6"/>
+      <c r="C5" s="11" t="n">
+        <f aca="false">B5-B4</f>
+        <v>-76.6</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <f aca="false">B5*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <f aca="false">C5*2.204623</f>
+        <v>-168.8741218</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <f aca="false">A5</f>
+        <v>46179</v>
+      </c>
+      <c r="G5" s="7"/>
+      <c r="I5" s="12" t="e">
+        <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>46176</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>77.5</v>
+      </c>
+      <c r="M5" s="10" t="n">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="n">
+        <v>46180</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="11" t="n">
+        <f aca="false">B6-B5</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <f aca="false">B6*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <f aca="false">C6*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <f aca="false">A6</f>
+        <v>46180</v>
+      </c>
+      <c r="G6" s="7"/>
+      <c r="H6" s="6"/>
+      <c r="K6" s="8" t="n">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>46177</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>77</v>
+      </c>
+      <c r="M6" s="10" t="n">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="11" t="n">
+        <f aca="false">B7-B6</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <f aca="false">B7*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <f aca="false">C7*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <f aca="false">A7</f>
+        <v>46181</v>
+      </c>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
+        <v>46178</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
+        <v>76.6</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="11" t="n">
+        <f aca="false">B8-B7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <f aca="false">B8*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <f aca="false">C8*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <f aca="false">A8</f>
+        <v>46182</v>
+      </c>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="11" t="n">
+        <f aca="false">B9-B8</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <f aca="false">B9*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <f aca="false">C9*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <f aca="false">A9</f>
+        <v>46183</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <f aca="false">AVERAGE(B2:B9)</f>
+        <v>77.0333333333333</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B10" s="6"/>
+      <c r="C10" s="11" t="n">
+        <f aca="false">B10-B9</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <f aca="false">B10*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <f aca="false">C10*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <f aca="false">A10</f>
+        <v>46184</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <f aca="false">AVERAGE(B3:B10)</f>
+        <v>76.8</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J10" s="3" t="e">
+        <f aca="false">((I5 - I7) * 7000) / J9</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="n">
+        <v>46185</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <f aca="false">B11-B10</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <f aca="false">B11*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <f aca="false">C11*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <f aca="false">A11</f>
+        <v>46185</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <f aca="false">AVERAGE(B4:B11)</f>
+        <v>76.6</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="n">
+        <v>46186</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <f aca="false">B12-B11</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <f aca="false">B12*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <f aca="false">C12*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <f aca="false">A12</f>
+        <v>46186</v>
+      </c>
+      <c r="G12" s="7" t="e">
+        <f aca="false">AVERAGE(B5:B12)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="n">
+        <v>46187</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <f aca="false">B13-B12</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <f aca="false">B13*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <f aca="false">C13*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <f aca="false">A13</f>
+        <v>46187</v>
+      </c>
+      <c r="G13" s="7" t="e">
+        <f aca="false">AVERAGE(B6:B13)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="n">
+        <v>46188</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <f aca="false">B14-B13</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <f aca="false">B14*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <f aca="false">C14*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <f aca="false">A14</f>
+        <v>46188</v>
+      </c>
+      <c r="G14" s="7" t="e">
+        <f aca="false">AVERAGE(B7:B14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="n">
+        <v>46189</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <f aca="false">B15-B14</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <f aca="false">B15*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <f aca="false">C15*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <f aca="false">A15</f>
+        <v>46189</v>
+      </c>
+      <c r="G15" s="7" t="e">
+        <f aca="false">AVERAGE(B8:B15)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="n">
+        <v>46190</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <f aca="false">B16-B15</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <f aca="false">B16*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <f aca="false">C16*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <f aca="false">A16</f>
+        <v>46190</v>
+      </c>
+      <c r="G16" s="7" t="e">
+        <f aca="false">AVERAGE(B9:B16)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="n">
+        <v>46191</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <f aca="false">B17-B16</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <f aca="false">B17*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <f aca="false">C17*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <f aca="false">A17</f>
+        <v>46191</v>
+      </c>
+      <c r="G17" s="7" t="e">
+        <f aca="false">AVERAGE(B10:B17)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="n">
+        <v>46192</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <f aca="false">B18-B17</f>
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <f aca="false">B18*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <f aca="false">C18*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <f aca="false">A18</f>
+        <v>46192</v>
+      </c>
+      <c r="G18" s="7" t="e">
+        <f aca="false">AVERAGE(B11:B18)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="n">
+        <v>46193</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <f aca="false">B19-B18</f>
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <f aca="false">B19*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <f aca="false">C19*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <f aca="false">A19</f>
+        <v>46193</v>
+      </c>
+      <c r="G19" s="7" t="e">
+        <f aca="false">AVERAGE(B12:B19)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="n">
+        <v>46194</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <f aca="false">B20-B19</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <f aca="false">B20*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <f aca="false">C20*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <f aca="false">A20</f>
+        <v>46194</v>
+      </c>
+      <c r="G20" s="7" t="e">
+        <f aca="false">AVERAGE(B13:B20)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="n">
+        <v>46195</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <f aca="false">B21-B20</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <f aca="false">B21*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <f aca="false">C21*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <f aca="false">A21</f>
+        <v>46195</v>
+      </c>
+      <c r="G21" s="7" t="e">
+        <f aca="false">AVERAGE(B14:B21)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="n">
+        <v>46196</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <f aca="false">B22-B21</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <f aca="false">B22*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <f aca="false">C22*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <f aca="false">A22</f>
+        <v>46196</v>
+      </c>
+      <c r="G22" s="7" t="e">
+        <f aca="false">AVERAGE(B15:B22)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="n">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <f aca="false">B23-B22</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <f aca="false">B23*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <f aca="false">C23*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <f aca="false">A23</f>
+        <v>46197</v>
+      </c>
+      <c r="G23" s="7" t="e">
+        <f aca="false">AVERAGE(B16:B23)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5" t="n">
+        <v>46198</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <f aca="false">B24-B23</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <f aca="false">B24*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <f aca="false">C24*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <f aca="false">A24</f>
+        <v>46198</v>
+      </c>
+      <c r="G24" s="7" t="e">
+        <f aca="false">AVERAGE(B17:B24)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="n">
+        <v>46199</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <f aca="false">B25-B24</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <f aca="false">B25*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <f aca="false">C25*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <f aca="false">A25</f>
+        <v>46199</v>
+      </c>
+      <c r="G25" s="7" t="e">
+        <f aca="false">AVERAGE(B18:B25)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="n">
+        <v>46200</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <f aca="false">B26-B25</f>
+        <v>0</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <f aca="false">B26*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <f aca="false">C26*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <f aca="false">A26</f>
+        <v>46200</v>
+      </c>
+      <c r="G26" s="7" t="e">
+        <f aca="false">AVERAGE(B19:B26)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="n">
+        <v>46201</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <f aca="false">B27-B26</f>
+        <v>0</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <f aca="false">B27*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <f aca="false">C27*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <f aca="false">A27</f>
+        <v>46201</v>
+      </c>
+      <c r="G27" s="7" t="e">
+        <f aca="false">AVERAGE(B20:B27)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="n">
+        <v>46202</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <f aca="false">B28-B27</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <f aca="false">B28*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <f aca="false">C28*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <f aca="false">A28</f>
+        <v>46202</v>
+      </c>
+      <c r="G28" s="7" t="e">
+        <f aca="false">AVERAGE(B21:B28)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <f aca="false">B29-B28</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <f aca="false">B29*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <f aca="false">C29*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <f aca="false">A29</f>
+        <v>46203</v>
+      </c>
+      <c r="G29" s="7" t="e">
+        <f aca="false">AVERAGE(B22:B29)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="n">
+        <v>46204</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <f aca="false">B30-B29</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <f aca="false">B30*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <f aca="false">C30*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <f aca="false">A30</f>
+        <v>46204</v>
+      </c>
+      <c r="G30" s="7" t="e">
+        <f aca="false">AVERAGE(B23:B30)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="L30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="n">
+        <v>46205</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <f aca="false">B31-B30</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <f aca="false">B31*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <f aca="false">C31*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <f aca="false">A31</f>
+        <v>46205</v>
+      </c>
+      <c r="G31" s="7" t="e">
+        <f aca="false">AVERAGE(B24:B31)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="n">
+        <v>46206</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <f aca="false">B32-B31</f>
+        <v>0</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <f aca="false">B32*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <f aca="false">C32*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <f aca="false">A32</f>
+        <v>46206</v>
+      </c>
+      <c r="G32" s="7" t="e">
+        <f aca="false">AVERAGE(B25:B32)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="n">
+        <v>46207</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <f aca="false">B33-B32</f>
+        <v>0</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <f aca="false">B33*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <f aca="false">C33*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <f aca="false">A33</f>
+        <v>46207</v>
+      </c>
+      <c r="G33" s="7" t="e">
+        <f aca="false">AVERAGE(B26:B33)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="n">
+        <v>46208</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <f aca="false">B34-B33</f>
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <f aca="false">B34*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <f aca="false">C34*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <f aca="false">A34</f>
+        <v>46208</v>
+      </c>
+      <c r="G34" s="7" t="e">
+        <f aca="false">AVERAGE(B27:B34)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="n">
+        <v>46209</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <f aca="false">B35-B34</f>
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <f aca="false">B35*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <f aca="false">C35*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <f aca="false">A35</f>
+        <v>46209</v>
+      </c>
+      <c r="G35" s="7" t="e">
+        <f aca="false">AVERAGE(B28:B35)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5"/>
+      <c r="C36" s="11"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5"/>
+      <c r="C37" s="11"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="7"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5"/>
+      <c r="C38" s="11"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5"/>
+      <c r="C39" s="11"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="7"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5"/>
+      <c r="C40" s="11"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5"/>
+      <c r="C41" s="11"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5"/>
+      <c r="C42" s="11"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5"/>
+      <c r="C43" s="11"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="7"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5"/>
+      <c r="C44" s="11"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="7"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5"/>
+      <c r="C45" s="11"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5"/>
+      <c r="C46" s="11"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="4"/>
+      <c r="G46" s="7"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5"/>
+      <c r="C47" s="11"/>
+      <c r="E47" s="7"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="7"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5"/>
+      <c r="C48" s="11"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="7"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5"/>
+      <c r="C49" s="11"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="7"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5"/>
+      <c r="C50" s="11"/>
+      <c r="E50" s="7"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="7"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5"/>
+      <c r="C51" s="11"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="7"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5"/>
+      <c r="C52" s="11"/>
+      <c r="E52" s="7"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="7"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5"/>
+      <c r="C53" s="11"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="5"/>
+      <c r="C54" s="11"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="7"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="5"/>
+      <c r="C55" s="11"/>
+      <c r="E55" s="7"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="7"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="5"/>
+      <c r="C56" s="11"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="7"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="5"/>
+      <c r="C57" s="11"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="7"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="5"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="11"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="7"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="5"/>
+      <c r="C59" s="11"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="7"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="5"/>
+      <c r="C60" s="11"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="7"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="5"/>
+      <c r="C61" s="11"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="7"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="5"/>
+      <c r="C62" s="11"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="7"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="5"/>
+      <c r="C63" s="11"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="7"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5"/>
+      <c r="C64" s="11"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="7"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="5"/>
+      <c r="C65" s="11"/>
+      <c r="E65" s="7"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="7"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="5"/>
+      <c r="C66" s="11"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="7"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="5"/>
+      <c r="C67" s="11"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="7"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="5"/>
+      <c r="C68" s="11"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="7"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="5"/>
+      <c r="C69" s="11"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="7"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="5"/>
+      <c r="C70" s="11"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="7"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="5"/>
+      <c r="C71" s="11"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="7"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="5"/>
+      <c r="C72" s="11"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="7"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="5"/>
+      <c r="C73" s="11"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="7"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="5"/>
+      <c r="C74" s="11"/>
+      <c r="E74" s="7"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="7"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="5"/>
+      <c r="B75" s="13"/>
+      <c r="C75" s="11"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="7"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="5"/>
+      <c r="C76" s="11"/>
+      <c r="E76" s="7"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="7"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="5"/>
+      <c r="C77" s="11"/>
+      <c r="E77" s="7"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="7"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="5"/>
+      <c r="C78" s="11"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="7"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="5"/>
+      <c r="C79" s="11"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="4"/>
+      <c r="G79" s="7"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="5"/>
+      <c r="C80" s="11"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="4"/>
+      <c r="G80" s="7"/>
+      <c r="I80" s="6"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="5"/>
+      <c r="C81" s="11"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="7"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="5"/>
+      <c r="C82" s="11"/>
+      <c r="E82" s="7"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="7"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="5"/>
+      <c r="C83" s="11"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="7"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="5"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="11"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="7"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="5"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="11"/>
+      <c r="E85" s="7"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="7"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="5"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="11"/>
+      <c r="E86" s="7"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="7"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="5"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="11"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="7"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="5"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="11"/>
+      <c r="E88" s="7"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="7"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="5"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="11"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="7"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="5"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="11"/>
+      <c r="E90" s="7"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="7"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5"/>
+      <c r="C91" s="11"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5"/>
+      <c r="C92" s="11"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="4"/>
+      <c r="G92" s="7"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5"/>
+      <c r="C93" s="11"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="7"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5"/>
+      <c r="C94" s="11"/>
+      <c r="E94" s="7"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="7"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="5"/>
+      <c r="C95" s="11"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="7"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="5"/>
+      <c r="C96" s="11"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="7"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="5"/>
+      <c r="C97" s="11"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="7"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="5"/>
+      <c r="C98" s="11"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="7"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5"/>
+      <c r="C99" s="11"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="7"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5"/>
+      <c r="C100" s="11"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="7"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5"/>
+      <c r="C101" s="11"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="7"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5"/>
+      <c r="C102" s="11"/>
+      <c r="E102" s="7"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="7"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5"/>
+      <c r="C103" s="11"/>
+      <c r="E103" s="7"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="7"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="5"/>
+      <c r="C104" s="11"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="7"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="5"/>
+      <c r="C105" s="11"/>
+      <c r="E105" s="7"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="7"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5"/>
+      <c r="C106" s="11"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="7"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="5"/>
+      <c r="C107" s="11"/>
+      <c r="E107" s="7"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="7"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5"/>
+      <c r="C108" s="11"/>
+      <c r="E108" s="7"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="7"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5"/>
+      <c r="C109" s="11"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5"/>
+      <c r="C110" s="11"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="7"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="5"/>
+      <c r="C111" s="11"/>
+      <c r="E111" s="7"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="7"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="1" right="1" top="1.66666666666667" bottom="1.66666666666667" header="1" footer="1"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Sans,Regular"&amp;K000000&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Sans,Regular"&amp;K000000Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
+      <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup xr2:uid="{EBD9D27C-ED44-46A8-98A4-00512C89C34D}">
+          <x14:colorSeries rgb="FF2A6099"/>
+          <x14:colorNegative rgb="FFFF0000"/>
+          <x14:colorAxis rgb="FFFF0000"/>
+          <x14:colorMarkers rgb="FFFF0000"/>
+          <x14:colorFirst rgb="FFFF0000"/>
+          <x14:colorLast rgb="FFFF0000"/>
+          <x14:colorHigh rgb="FFFF0000"/>
+          <x14:colorLow rgb="FFFF0000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sheet1!B1:B1048576</xm:f>
+              <xm:sqref>A1</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B2</xm:f>
+              <xm:sqref>A2</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B3</xm:f>
+              <xm:sqref>A3</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B4</xm:f>
+              <xm:sqref>A4</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B5</xm:f>
+              <xm:sqref>A5</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B6</xm:f>
+              <xm:sqref>A6</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B7</xm:f>
+              <xm:sqref>A7</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B8</xm:f>
+              <xm:sqref>A8</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B9</xm:f>
+              <xm:sqref>A9</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B10</xm:f>
+              <xm:sqref>A10</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B11</xm:f>
+              <xm:sqref>A11</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B12</xm:f>
+              <xm:sqref>A12</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B13</xm:f>
+              <xm:sqref>A13</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B14</xm:f>
+              <xm:sqref>A14</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B15</xm:f>
+              <xm:sqref>A15</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B16</xm:f>
+              <xm:sqref>A16</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B17</xm:f>
+              <xm:sqref>A17</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B18</xm:f>
+              <xm:sqref>A18</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B19</xm:f>
+              <xm:sqref>A20</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B20</xm:f>
+              <xm:sqref>A21</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B21</xm:f>
+              <xm:sqref>A22</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B22</xm:f>
+              <xm:sqref>A23</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B23</xm:f>
+              <xm:sqref>A24</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B24</xm:f>
+              <xm:sqref>A25</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B25</xm:f>
+              <xm:sqref>A26</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B26</xm:f>
+              <xm:sqref>A27</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B27</xm:f>
+              <xm:sqref>A28</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B28</xm:f>
+              <xm:sqref>A29</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B29</xm:f>
+              <xm:sqref>A30</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B30</xm:f>
+              <xm:sqref>A31</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B31</xm:f>
+              <xm:sqref>A32</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B32</xm:f>
+              <xm:sqref>A33</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B33</xm:f>
+              <xm:sqref>A34</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B34</xm:f>
+              <xm:sqref>A35</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+      </x14:sparklineGroups>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr defaultColWidth="69.328125" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.35"/>
@@ -1397,22 +3593,22 @@
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>2</v>
       </c>
       <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46127</v>
+        <v>46143</v>
       </c>
       <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.1</v>
+        <v>76</v>
       </c>
       <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.6125</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1441,15 +3637,15 @@
       <c r="G2" s="7"/>
       <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46128</v>
+        <v>46144</v>
       </c>
       <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.1</v>
+        <v>76</v>
       </c>
       <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.5125</v>
+        <v>75.5625</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,15 +3674,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46129</v>
+        <v>46145</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.1</v>
+        <v>76</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.45</v>
+        <v>75.6875</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1514,23 +3710,23 @@
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.1</v>
+        <v>76</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46130</v>
+        <v>46146</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>74.8</v>
+        <v>76</v>
       </c>
       <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.3875</v>
+        <v>75.6125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,19 +3758,19 @@
       </c>
       <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>75.1142857142857</v>
+        <v>76.2285714285714</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46131</v>
+        <v>46147</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.1</v>
+        <v>76</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.525</v>
+        <v>75.6125</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1604,15 +3800,15 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46132</v>
+        <v>46148</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>75.2</v>
+        <v>77</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.4125</v>
+        <v>75.7875</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1640,22 +3836,22 @@
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>70</v>
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46133</v>
+        <v>46149</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>74.4</v>
+        <v>76.6</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>75.15</v>
+        <v>75.9875</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1711,10 +3907,10 @@
         <v>77.0125</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1000</v>
@@ -1748,14 +3944,14 @@
         <v>76.9875</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>35.8</v>
+        <v>43.6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1786,7 +3982,7 @@
         <v>77.05</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1817,7 +4013,7 @@
         <v>77.2125</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2016,7 +4212,7 @@
         <v>77.7</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2215,7 +4411,7 @@
         <v>76.9</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2415,7 +4611,7 @@
         <v>75.95</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2614,7 +4810,7 @@
         <v>75.7</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2813,7 +5009,7 @@
         <v>75.2375</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2956,7 +5152,7 @@
         <v>74.8625</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2987,7 +5183,7 @@
         <v>74.9125</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3018,7 +5214,7 @@
         <v>75.025</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3049,7 +5245,7 @@
         <v>75.125</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3080,7 +5276,7 @@
         <v>75.05</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3138,6 +5334,9 @@
         <f aca="false">AVERAGE(B51:B58)</f>
         <v>75.3</v>
       </c>
+      <c r="H58" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5" t="n">
@@ -3223,7 +5422,7 @@
         <v>75.7</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3421,6 +5620,9 @@
         <f aca="false">AVERAGE(B61:B68)</f>
         <v>75.3875</v>
       </c>
+      <c r="H68" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5" t="n">
@@ -3510,17 +5712,20 @@
       <c r="A72" s="5" t="n">
         <v>46134</v>
       </c>
+      <c r="B72" s="1" t="n">
+        <v>73.8</v>
+      </c>
       <c r="C72" s="11" t="n">
         <f aca="false">B72-B71</f>
-        <v>-74.4</v>
+        <v>-0.600000000000009</v>
       </c>
       <c r="D72" s="3" t="n">
         <f aca="false">B72*2.204623</f>
-        <v>0</v>
+        <v>162.7011774</v>
       </c>
       <c r="E72" s="7" t="n">
         <f aca="false">C72*2.204623</f>
-        <v>-164.0239512</v>
+        <v>-1.32277380000002</v>
       </c>
       <c r="F72" s="4" t="n">
         <f aca="false">A72</f>
@@ -3528,24 +5733,27 @@
       </c>
       <c r="G72" s="7" t="n">
         <f aca="false">AVERAGE(B65:B72)</f>
-        <v>75.1142857142857</v>
+        <v>74.95</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5" t="n">
         <v>46135</v>
       </c>
+      <c r="B73" s="1" t="n">
+        <v>74.2</v>
+      </c>
       <c r="C73" s="11" t="n">
         <f aca="false">B73-B72</f>
-        <v>0</v>
+        <v>0.400000000000006</v>
       </c>
       <c r="D73" s="3" t="n">
         <f aca="false">B73*2.204623</f>
-        <v>0</v>
+        <v>163.5830266</v>
       </c>
       <c r="E73" s="7" t="n">
         <f aca="false">C73*2.204623</f>
-        <v>0</v>
+        <v>0.881849200000013</v>
       </c>
       <c r="F73" s="4" t="n">
         <f aca="false">A73</f>
@@ -3553,24 +5761,27 @@
       </c>
       <c r="G73" s="7" t="n">
         <f aca="false">AVERAGE(B66:B73)</f>
-        <v>75.1166666666667</v>
+        <v>74.8375</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5" t="n">
         <v>46136</v>
       </c>
+      <c r="B74" s="1" t="n">
+        <v>73.9</v>
+      </c>
       <c r="C74" s="11" t="n">
         <f aca="false">B74-B73</f>
-        <v>0</v>
+        <v>-0.299999999999997</v>
       </c>
       <c r="D74" s="3" t="n">
         <f aca="false">B74*2.204623</f>
-        <v>0</v>
+        <v>162.9216397</v>
       </c>
       <c r="E74" s="7" t="n">
         <f aca="false">C74*2.204623</f>
-        <v>0</v>
+        <v>-0.661386899999994</v>
       </c>
       <c r="F74" s="4" t="n">
         <f aca="false">A74</f>
@@ -3578,25 +5789,27 @@
       </c>
       <c r="G74" s="7" t="n">
         <f aca="false">AVERAGE(B67:B74)</f>
-        <v>75.12</v>
+        <v>74.6875</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5" t="n">
         <v>46137</v>
       </c>
-      <c r="B75" s="13"/>
+      <c r="B75" s="13" t="n">
+        <v>75</v>
+      </c>
       <c r="C75" s="11" t="n">
         <f aca="false">B75-B74</f>
-        <v>0</v>
+        <v>1.09999999999999</v>
       </c>
       <c r="D75" s="3" t="n">
         <f aca="false">B75*2.204623</f>
-        <v>0</v>
+        <v>165.346725</v>
       </c>
       <c r="E75" s="7" t="n">
         <f aca="false">C75*2.204623</f>
-        <v>0</v>
+        <v>2.42508529999999</v>
       </c>
       <c r="F75" s="4" t="n">
         <f aca="false">A75</f>
@@ -3604,24 +5817,30 @@
       </c>
       <c r="G75" s="7" t="n">
         <f aca="false">AVERAGE(B68:B75)</f>
-        <v>75.125</v>
+        <v>74.675</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5" t="n">
         <v>46138</v>
       </c>
+      <c r="B76" s="1" t="n">
+        <v>76.6</v>
+      </c>
       <c r="C76" s="11" t="n">
         <f aca="false">B76-B75</f>
-        <v>0</v>
+        <v>1.59999999999999</v>
       </c>
       <c r="D76" s="3" t="n">
         <f aca="false">B76*2.204623</f>
-        <v>0</v>
+        <v>168.8741218</v>
       </c>
       <c r="E76" s="7" t="n">
         <f aca="false">C76*2.204623</f>
-        <v>0</v>
+        <v>3.52739679999999</v>
       </c>
       <c r="F76" s="4" t="n">
         <f aca="false">A76</f>
@@ -3629,24 +5848,27 @@
       </c>
       <c r="G76" s="7" t="n">
         <f aca="false">AVERAGE(B69:B76)</f>
-        <v>75.2333333333333</v>
+        <v>74.9</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5" t="n">
         <v>46139</v>
       </c>
+      <c r="B77" s="1" t="n">
+        <v>76</v>
+      </c>
       <c r="C77" s="11" t="n">
         <f aca="false">B77-B76</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D77" s="3" t="n">
         <f aca="false">B77*2.204623</f>
-        <v>0</v>
+        <v>167.551348</v>
       </c>
       <c r="E77" s="7" t="n">
         <f aca="false">C77*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F77" s="4" t="n">
         <f aca="false">A77</f>
@@ -3654,24 +5876,27 @@
       </c>
       <c r="G77" s="7" t="n">
         <f aca="false">AVERAGE(B70:B77)</f>
-        <v>74.8</v>
+        <v>74.8875</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5" t="n">
         <v>46140</v>
       </c>
+      <c r="B78" s="1" t="n">
+        <v>75.6</v>
+      </c>
       <c r="C78" s="11" t="n">
         <f aca="false">B78-B77</f>
-        <v>0</v>
+        <v>-0.400000000000006</v>
       </c>
       <c r="D78" s="3" t="n">
         <f aca="false">B78*2.204623</f>
-        <v>0</v>
+        <v>166.6694988</v>
       </c>
       <c r="E78" s="7" t="n">
         <f aca="false">C78*2.204623</f>
-        <v>0</v>
+        <v>-0.881849200000013</v>
       </c>
       <c r="F78" s="4" t="n">
         <f aca="false">A78</f>
@@ -3679,129 +5904,888 @@
       </c>
       <c r="G78" s="7" t="n">
         <f aca="false">AVERAGE(B71:B78)</f>
-        <v>74.4</v>
+        <v>74.9375</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5" t="n">
         <v>46141</v>
       </c>
+      <c r="B79" s="1" t="n">
+        <v>75</v>
+      </c>
       <c r="C79" s="11" t="n">
         <f aca="false">B79-B78</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D79" s="3" t="n">
         <f aca="false">B79*2.204623</f>
-        <v>0</v>
+        <v>165.346725</v>
       </c>
       <c r="E79" s="7" t="n">
         <f aca="false">C79*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F79" s="4" t="n">
         <f aca="false">A79</f>
         <v>46141</v>
       </c>
-      <c r="G79" s="7" t="e">
+      <c r="G79" s="7" t="n">
         <f aca="false">AVERAGE(B72:B79)</f>
-        <v>#DIV/0!</v>
+        <v>75.0125</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5" t="n">
         <v>46142</v>
       </c>
+      <c r="B80" s="1" t="n">
+        <v>74.3</v>
+      </c>
       <c r="C80" s="11" t="n">
         <f aca="false">B80-B79</f>
-        <v>0</v>
+        <v>-0.700000000000003</v>
       </c>
       <c r="D80" s="3" t="n">
         <f aca="false">B80*2.204623</f>
-        <v>0</v>
+        <v>163.8034889</v>
       </c>
       <c r="E80" s="7" t="n">
         <f aca="false">C80*2.204623</f>
-        <v>0</v>
-      </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="7"/>
+        <v>-1.54323610000001</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <f aca="false">A80</f>
+        <v>46142</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <f aca="false">AVERAGE(B73:B80)</f>
+        <v>75.075</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I80" s="6"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5"/>
-      <c r="C81" s="11"/>
-      <c r="E81" s="7"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="7"/>
+      <c r="A81" s="5" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <f aca="false">B81-B80</f>
+        <v>1.7</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <f aca="false">B81*2.204623</f>
+        <v>167.551348</v>
+      </c>
+      <c r="E81" s="7" t="n">
+        <f aca="false">C81*2.204623</f>
+        <v>3.74785910000001</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <f aca="false">A81</f>
+        <v>46143</v>
+      </c>
+      <c r="G81" s="7" t="n">
+        <f aca="false">AVERAGE(B74:B81)</f>
+        <v>75.3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5"/>
-      <c r="C82" s="11"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="7"/>
+      <c r="A82" s="5" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <f aca="false">B82-B81</f>
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <f aca="false">B82*2.204623</f>
+        <v>167.551348</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <f aca="false">C82*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <f aca="false">A82</f>
+        <v>46144</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <f aca="false">AVERAGE(B75:B82)</f>
+        <v>75.5625</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5"/>
-      <c r="C83" s="11"/>
-      <c r="E83" s="7"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="7"/>
+      <c r="A83" s="5" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="C83" s="11" t="n">
+        <f aca="false">B83-B82</f>
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <f aca="false">B83*2.204623</f>
+        <v>167.551348</v>
+      </c>
+      <c r="E83" s="7" t="n">
+        <f aca="false">C83*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <f aca="false">A83</f>
+        <v>46145</v>
+      </c>
+      <c r="G83" s="7" t="n">
+        <f aca="false">AVERAGE(B76:B83)</f>
+        <v>75.6875</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="11"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="7"/>
+      <c r="A84" s="5" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B84" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <f aca="false">B84-B83</f>
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <f aca="false">B84*2.204623</f>
+        <v>167.551348</v>
+      </c>
+      <c r="E84" s="7" t="n">
+        <f aca="false">C84*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <f aca="false">A84</f>
+        <v>46146</v>
+      </c>
+      <c r="G84" s="7" t="n">
+        <f aca="false">AVERAGE(B77:B84)</f>
+        <v>75.6125</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="11"/>
-      <c r="E85" s="7"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="7"/>
+      <c r="A85" s="5" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B85" s="6" t="n">
+        <v>76</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <f aca="false">B85-B84</f>
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <f aca="false">B85*2.204623</f>
+        <v>167.551348</v>
+      </c>
+      <c r="E85" s="7" t="n">
+        <f aca="false">C85*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <f aca="false">A85</f>
+        <v>46147</v>
+      </c>
+      <c r="G85" s="7" t="n">
+        <f aca="false">AVERAGE(B78:B85)</f>
+        <v>75.6125</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="11"/>
-      <c r="E86" s="7"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="7"/>
+      <c r="A86" s="5" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <f aca="false">B86-B85</f>
+        <v>1</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <f aca="false">B86*2.204623</f>
+        <v>169.755971</v>
+      </c>
+      <c r="E86" s="7" t="n">
+        <f aca="false">C86*2.204623</f>
+        <v>2.204623</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <f aca="false">A86</f>
+        <v>46148</v>
+      </c>
+      <c r="G86" s="7" t="n">
+        <f aca="false">AVERAGE(B79:B86)</f>
+        <v>75.7875</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="11"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="7"/>
+      <c r="A87" s="5" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>76.6</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <f aca="false">B87-B86</f>
+        <v>-0.400000000000006</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <f aca="false">B87*2.204623</f>
+        <v>168.8741218</v>
+      </c>
+      <c r="E87" s="7" t="n">
+        <f aca="false">C87*2.204623</f>
+        <v>-0.881849200000013</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <f aca="false">A87</f>
+        <v>46149</v>
+      </c>
+      <c r="G87" s="7" t="n">
+        <f aca="false">AVERAGE(B80:B87)</f>
+        <v>75.9875</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5"/>
+      <c r="A88" s="5" t="n">
+        <v>46150</v>
+      </c>
       <c r="B88" s="6"/>
-      <c r="C88" s="11"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="7"/>
+      <c r="C88" s="11" t="n">
+        <f aca="false">B88-B87</f>
+        <v>-76.6</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <f aca="false">B88*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E88" s="7" t="n">
+        <f aca="false">C88*2.204623</f>
+        <v>-168.8741218</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <f aca="false">A88</f>
+        <v>46150</v>
+      </c>
+      <c r="G88" s="7" t="n">
+        <f aca="false">AVERAGE(B81:B88)</f>
+        <v>76.2285714285714</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5"/>
+      <c r="A89" s="5" t="n">
+        <v>46151</v>
+      </c>
       <c r="B89" s="6"/>
-      <c r="C89" s="11"/>
-      <c r="E89" s="7"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="7"/>
+      <c r="C89" s="11" t="n">
+        <f aca="false">B89-B88</f>
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <f aca="false">B89*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E89" s="7" t="n">
+        <f aca="false">C89*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <f aca="false">A89</f>
+        <v>46151</v>
+      </c>
+      <c r="G89" s="7" t="n">
+        <f aca="false">AVERAGE(B82:B89)</f>
+        <v>76.2666666666667</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5"/>
+      <c r="A90" s="5" t="n">
+        <v>46152</v>
+      </c>
       <c r="B90" s="6"/>
-      <c r="C90" s="11"/>
-      <c r="E90" s="7"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="7"/>
+      <c r="C90" s="11" t="n">
+        <f aca="false">B90-B89</f>
+        <v>0</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <f aca="false">B90*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E90" s="7" t="n">
+        <f aca="false">C90*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <f aca="false">A90</f>
+        <v>46152</v>
+      </c>
+      <c r="G90" s="7" t="n">
+        <f aca="false">AVERAGE(B83:B90)</f>
+        <v>76.32</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="5" t="n">
+        <v>46153</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <f aca="false">B91-B90</f>
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <f aca="false">B91*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E91" s="7" t="n">
+        <f aca="false">C91*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <f aca="false">A91</f>
+        <v>46153</v>
+      </c>
+      <c r="G91" s="7" t="n">
+        <f aca="false">AVERAGE(B84:B91)</f>
+        <v>76.4</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="5" t="n">
+        <v>46154</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <f aca="false">B92-B91</f>
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <f aca="false">B92*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E92" s="7" t="n">
+        <f aca="false">C92*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <f aca="false">A92</f>
+        <v>46154</v>
+      </c>
+      <c r="G92" s="7" t="n">
+        <f aca="false">AVERAGE(B85:B92)</f>
+        <v>76.5333333333333</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5" t="n">
+        <v>46155</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <f aca="false">B93-B92</f>
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <f aca="false">B93*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E93" s="7" t="n">
+        <f aca="false">C93*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <f aca="false">A93</f>
+        <v>46155</v>
+      </c>
+      <c r="G93" s="7" t="n">
+        <f aca="false">AVERAGE(B86:B93)</f>
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="5" t="n">
+        <v>46156</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <f aca="false">B94-B93</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <f aca="false">B94*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="7" t="n">
+        <f aca="false">C94*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <f aca="false">A94</f>
+        <v>46156</v>
+      </c>
+      <c r="G94" s="7" t="n">
+        <f aca="false">AVERAGE(B87:B94)</f>
+        <v>76.6</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A95" s="5" t="n">
+        <v>46157</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <f aca="false">B95-B94</f>
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <f aca="false">B95*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E95" s="7" t="n">
+        <f aca="false">C95*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <f aca="false">A95</f>
+        <v>46157</v>
+      </c>
+      <c r="G95" s="7" t="e">
+        <f aca="false">AVERAGE(B88:B95)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="5" t="n">
+        <v>46158</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <f aca="false">B96-B95</f>
+        <v>0</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <f aca="false">B96*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E96" s="7" t="n">
+        <f aca="false">C96*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <f aca="false">A96</f>
+        <v>46158</v>
+      </c>
+      <c r="G96" s="7" t="e">
+        <f aca="false">AVERAGE(B89:B96)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A97" s="5" t="n">
+        <v>46159</v>
+      </c>
+      <c r="C97" s="11" t="n">
+        <f aca="false">B97-B96</f>
+        <v>0</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <f aca="false">B97*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E97" s="7" t="n">
+        <f aca="false">C97*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <f aca="false">A97</f>
+        <v>46159</v>
+      </c>
+      <c r="G97" s="7" t="e">
+        <f aca="false">AVERAGE(B90:B97)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="5" t="n">
+        <v>46160</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <f aca="false">B98-B97</f>
+        <v>0</v>
+      </c>
+      <c r="D98" s="3" t="n">
+        <f aca="false">B98*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E98" s="7" t="n">
+        <f aca="false">C98*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <f aca="false">A98</f>
+        <v>46160</v>
+      </c>
+      <c r="G98" s="7" t="e">
+        <f aca="false">AVERAGE(B91:B98)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="5" t="n">
+        <v>46161</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <f aca="false">B99-B98</f>
+        <v>0</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <f aca="false">B99*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E99" s="7" t="n">
+        <f aca="false">C99*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <f aca="false">A99</f>
+        <v>46161</v>
+      </c>
+      <c r="G99" s="7" t="e">
+        <f aca="false">AVERAGE(B92:B99)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <f aca="false">B100-B99</f>
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <f aca="false">B100*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E100" s="7" t="n">
+        <f aca="false">C100*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <f aca="false">A100</f>
+        <v>46162</v>
+      </c>
+      <c r="G100" s="7" t="e">
+        <f aca="false">AVERAGE(B93:B100)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <f aca="false">B101-B100</f>
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <f aca="false">B101*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E101" s="7" t="n">
+        <f aca="false">C101*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <f aca="false">A101</f>
+        <v>46163</v>
+      </c>
+      <c r="G101" s="7" t="e">
+        <f aca="false">AVERAGE(B94:B101)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <f aca="false">B102-B101</f>
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <f aca="false">B102*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E102" s="7" t="n">
+        <f aca="false">C102*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <f aca="false">A102</f>
+        <v>46164</v>
+      </c>
+      <c r="G102" s="7" t="e">
+        <f aca="false">AVERAGE(B95:B102)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <f aca="false">B103-B102</f>
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <f aca="false">B103*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E103" s="7" t="n">
+        <f aca="false">C103*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <f aca="false">A103</f>
+        <v>46165</v>
+      </c>
+      <c r="G103" s="7" t="e">
+        <f aca="false">AVERAGE(B96:B103)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <f aca="false">B104-B103</f>
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <f aca="false">B104*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E104" s="7" t="n">
+        <f aca="false">C104*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <f aca="false">A104</f>
+        <v>46166</v>
+      </c>
+      <c r="G104" s="7" t="e">
+        <f aca="false">AVERAGE(B97:B104)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="5" t="n">
+        <v>46167</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <f aca="false">B105-B104</f>
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <f aca="false">B105*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E105" s="7" t="n">
+        <f aca="false">C105*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <f aca="false">A105</f>
+        <v>46167</v>
+      </c>
+      <c r="G105" s="7" t="e">
+        <f aca="false">AVERAGE(B98:B105)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <f aca="false">B106-B105</f>
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <f aca="false">B106*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E106" s="7" t="n">
+        <f aca="false">C106*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <f aca="false">A106</f>
+        <v>46168</v>
+      </c>
+      <c r="G106" s="7" t="e">
+        <f aca="false">AVERAGE(B99:B106)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <f aca="false">B107-B106</f>
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <f aca="false">B107*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E107" s="7" t="n">
+        <f aca="false">C107*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <f aca="false">A107</f>
+        <v>46169</v>
+      </c>
+      <c r="G107" s="7" t="e">
+        <f aca="false">AVERAGE(B100:B107)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <f aca="false">B108-B107</f>
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <f aca="false">B108*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E108" s="7" t="n">
+        <f aca="false">C108*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <f aca="false">A108</f>
+        <v>46170</v>
+      </c>
+      <c r="G108" s="7" t="e">
+        <f aca="false">AVERAGE(B101:B108)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <f aca="false">B109-B108</f>
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <f aca="false">B109*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E109" s="7" t="n">
+        <f aca="false">C109*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <f aca="false">A109</f>
+        <v>46171</v>
+      </c>
+      <c r="G109" s="7" t="e">
+        <f aca="false">AVERAGE(B102:B109)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <f aca="false">B110-B109</f>
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <f aca="false">B110*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E110" s="7" t="n">
+        <f aca="false">C110*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <f aca="false">A110</f>
+        <v>46172</v>
+      </c>
+      <c r="G110" s="7" t="e">
+        <f aca="false">AVERAGE(B103:B110)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <f aca="false">B111-B110</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <f aca="false">B111*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E111" s="7" t="n">
+        <f aca="false">C111*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <f aca="false">A111</f>
+        <v>46173</v>
+      </c>
+      <c r="G111" s="7" t="e">
+        <f aca="false">AVERAGE(B104:B111)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3837,7 +6821,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -3992,7 +6976,7 @@
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
@@ -4080,7 +7064,7 @@
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3" t="n">
         <f aca="false">I5-I8</f>
@@ -4127,7 +7111,7 @@
         <v>85.8571428571429</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">102-I5</f>
@@ -4174,7 +7158,7 @@
         <v>85.7857142857143</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>75</v>

--- a/tracker.xlsx
+++ b/tracker.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t xml:space="preserve">7 day average</t>
   </si>
@@ -44,10 +44,25 @@
     <t xml:space="preserve">Last 7 values</t>
   </si>
   <si>
+    <t xml:space="preserve">earlier weighin</t>
+  </si>
+  <si>
     <t xml:space="preserve">DAILY CALORIE DEFICIT</t>
   </si>
   <si>
     <t xml:space="preserve">remaining rfl ~days:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">massive meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">corn day :)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maintanence start</t>
   </si>
   <si>
     <t xml:space="preserve">Day 2 of rfl</t>
@@ -335,10 +350,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0824237335572348"/>
-          <c:y val="0.0669707500724008"/>
-          <c:w val="0.704729918835712"/>
-          <c:h val="0.853605560382276"/>
+          <c:x val="0.0825199645075422"/>
+          <c:y val="0.0670921882933198"/>
+          <c:w val="0.704385186568907"/>
+          <c:h val="0.85152680060927"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -424,25 +439,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Err:502</c:v>
+                  <c:v>Thursday</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Err:502</c:v>
+                  <c:v>Friday</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Thursday</c:v>
+                  <c:v>Saturday</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Tuesday</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Friday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -453,20 +468,26 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>76.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>77.3</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>77</c:v>
+                  <c:v>76.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80.3</c:v>
+                  <c:v>77.7</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.5</c:v>
+                  <c:v>77.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>77</c:v>
+                  <c:v>76.3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>76.6</c:v>
+                  <c:v>76.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -553,25 +574,25 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Err:502</c:v>
+                  <c:v>Thursday</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Err:502</c:v>
+                  <c:v>Friday</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Thursday</c:v>
+                  <c:v>Saturday</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>Sunday</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Monday</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Tuesday</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="6">
                   <c:v>Wednesday</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Thursday</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Friday</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -582,17 +603,26 @@
               <c:numCache>
                 <c:formatCode>[BLUE]0.00;[RED]\-0.00</c:formatCode>
                 <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>76.7125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>76.9125</c:v>
+                </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>77.1875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>77.1125</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>77.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>76.9125</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>76.9375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -607,11 +637,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="6972484"/>
-        <c:axId val="41247786"/>
+        <c:axId val="2202419"/>
+        <c:axId val="64810016"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6972484"/>
+        <c:axId val="2202419"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -644,15 +674,15 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41247786"/>
-        <c:crossesAt val="0"/>
+        <c:crossAx val="64810016"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41247786"/>
+        <c:axId val="64810016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -694,7 +724,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6972484"/>
+        <c:crossAx val="2202419"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -713,10 +743,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.803180637982196"/>
-          <c:y val="0.303162877429535"/>
-          <c:w val="0.188473664688427"/>
-          <c:h val="0.0844151186975543"/>
+          <c:x val="0.803172381618848"/>
+          <c:y val="0.303135636179303"/>
+          <c:w val="0.188438928804703"/>
+          <c:h val="0.0843713789107764"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -769,10 +799,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0824237335572348"/>
-          <c:y val="0.0669707500724008"/>
-          <c:w val="0.704683272693348"/>
-          <c:h val="0.853605560382276"/>
+          <c:x val="0.0825199645075422"/>
+          <c:y val="0.0670921882933198"/>
+          <c:w val="0.704338485966469"/>
+          <c:h val="0.85152680060927"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1034,11 +1064,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="70112705"/>
-        <c:axId val="73294654"/>
+        <c:axId val="65672328"/>
+        <c:axId val="11189070"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="70112705"/>
+        <c:axId val="65672328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1071,7 +1101,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73294654"/>
+        <c:crossAx val="11189070"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1079,7 +1109,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73294654"/>
+        <c:axId val="11189070"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1121,7 +1151,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70112705"/>
+        <c:crossAx val="65672328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1140,10 +1170,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.803106633081444"/>
-          <c:y val="0.303069794381697"/>
-          <c:w val="0.188459206045622"/>
-          <c:h val="0.0843530519151401"/>
+          <c:x val="0.803079076277117"/>
+          <c:y val="0.303063219639366"/>
+          <c:w val="0.188438928804703"/>
+          <c:h val="0.0842989571263036"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1196,10 +1226,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.0823809301674675"/>
-          <c:y val="0.0669901506373117"/>
-          <c:w val="0.704762793301302"/>
-          <c:h val="0.853635573580533"/>
+          <c:x val="0.0824771156360919"/>
+          <c:y val="0.0671116592904302"/>
+          <c:w val="0.704418083317766"/>
+          <c:h val="0.851556264964086"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1461,11 +1491,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="99048173"/>
-        <c:axId val="10742689"/>
+        <c:axId val="63872540"/>
+        <c:axId val="8375837"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="99048173"/>
+        <c:axId val="63872540"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1498,7 +1528,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10742689"/>
+        <c:crossAx val="8375837"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1506,7 +1536,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10742689"/>
+        <c:axId val="8375837"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1548,7 +1578,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99048173"/>
+        <c:crossAx val="63872540"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1567,10 +1597,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.803144096655316"/>
-          <c:y val="0.30308516801854"/>
-          <c:w val="0.188421347266281"/>
-          <c:h val="0.0843050626493807"/>
+          <c:x val="0.803116543808902"/>
+          <c:y val="0.303078594712061"/>
+          <c:w val="0.188401063780152"/>
+          <c:h val="0.0842509417560128"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1617,14 +1647,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>394560</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>664560</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:colOff>655560</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1632,8 +1662,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7717320" cy="4971960"/>
+        <a:off x="11475360" y="2255040"/>
+        <a:ext cx="7708320" cy="4962960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1652,14 +1682,14 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>394560</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>159480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>664560</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:colOff>655560</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>169560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1667,8 +1697,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="11475360" y="2618280"/>
-        <a:ext cx="7717320" cy="4971960"/>
+        <a:off x="11475360" y="2255040"/>
+        <a:ext cx="7708320" cy="4962960"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1687,14 +1717,14 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>712800</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>152640</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>119520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>51480</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>169920</xdr:rowOff>
+      <xdr:colOff>42480</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>127800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1702,8 +1732,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="9101160" y="1676520"/>
-        <a:ext cx="7716960" cy="4970520"/>
+        <a:off x="9101160" y="1452960"/>
+        <a:ext cx="7707960" cy="4961520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1868,17 +1898,17 @@
       <c r="J1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="8" t="e">
+      <c r="K1" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L1" s="9" t="e">
+        <v>46205</v>
+      </c>
+      <c r="L1" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M1" s="10" t="e">
+        <v>76.3</v>
+      </c>
+      <c r="M1" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>#VALUE!</v>
+        <v>76.7125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1905,17 +1935,17 @@
         <v>46176</v>
       </c>
       <c r="G2" s="7"/>
-      <c r="K2" s="8" t="e">
+      <c r="K2" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="L2" s="9" t="e">
+        <v>46206</v>
+      </c>
+      <c r="L2" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="M2" s="10" t="e">
+        <v>77.3</v>
+      </c>
+      <c r="M2" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>#VALUE!</v>
+        <v>76.9125</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1944,15 +1974,15 @@
       <c r="G3" s="7"/>
       <c r="K3" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46177</v>
+        <v>46207</v>
       </c>
       <c r="L3" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77</v>
+        <v>76.7</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>0</v>
+        <v>77.1875</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1980,78 +2010,82 @@
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="6"/>
-      <c r="I4" s="12" t="e">
+      <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>#VALUE!</v>
+        <v>76.7</v>
       </c>
       <c r="K4" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46175</v>
+        <v>46208</v>
       </c>
       <c r="L4" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>80.3</v>
-      </c>
-      <c r="M4" s="10" t="str">
+        <v>77.7</v>
+      </c>
+      <c r="M4" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>7 day average</v>
+        <v>77.1125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="n">
         <v>46179</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="6" t="n">
+        <v>76.3</v>
+      </c>
       <c r="C5" s="11" t="n">
         <f aca="false">B5-B4</f>
-        <v>-76.6</v>
+        <v>-0.299999999999997</v>
       </c>
       <c r="D5" s="3" t="n">
         <f aca="false">B5*2.204623</f>
-        <v>0</v>
+        <v>168.2127349</v>
       </c>
       <c r="E5" s="7" t="n">
         <f aca="false">C5*2.204623</f>
-        <v>-168.8741218</v>
+        <v>-0.661386899999994</v>
       </c>
       <c r="F5" s="4" t="n">
         <f aca="false">A5</f>
         <v>46179</v>
       </c>
       <c r="G5" s="7"/>
-      <c r="I5" s="12" t="e">
+      <c r="I5" s="12" t="n">
         <f aca="true">AVERAGE(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
-        <v>#VALUE!</v>
+        <v>76.9428571428572</v>
       </c>
       <c r="K5" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46176</v>
+        <v>46209</v>
       </c>
       <c r="L5" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77.5</v>
+        <v>77.6</v>
       </c>
       <c r="M5" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>0</v>
+        <v>77.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="n">
         <v>46180</v>
       </c>
-      <c r="B6" s="6"/>
+      <c r="B6" s="6" t="n">
+        <v>78.1</v>
+      </c>
       <c r="C6" s="11" t="n">
         <f aca="false">B6-B5</f>
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="D6" s="3" t="n">
         <f aca="false">B6*2.204623</f>
-        <v>0</v>
+        <v>172.1810563</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">C6*2.204623</f>
-        <v>0</v>
+        <v>3.96832139999999</v>
       </c>
       <c r="F6" s="4" t="n">
         <f aca="false">A6</f>
@@ -2061,33 +2095,35 @@
       <c r="H6" s="6"/>
       <c r="K6" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46177</v>
+        <v>46210</v>
       </c>
       <c r="L6" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>77</v>
+        <v>76.3</v>
       </c>
       <c r="M6" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>0</v>
+        <v>76.9125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="n">
         <v>46181</v>
       </c>
-      <c r="B7" s="6"/>
+      <c r="B7" s="6" t="n">
+        <v>76.2</v>
+      </c>
       <c r="C7" s="11" t="n">
         <f aca="false">B7-B6</f>
-        <v>0</v>
+        <v>-1.89999999999999</v>
       </c>
       <c r="D7" s="3" t="n">
         <f aca="false">B7*2.204623</f>
-        <v>0</v>
+        <v>167.9922726</v>
       </c>
       <c r="E7" s="7" t="n">
         <f aca="false">C7*2.204623</f>
-        <v>0</v>
+        <v>-4.18878369999998</v>
       </c>
       <c r="F7" s="4" t="n">
         <f aca="false">A7</f>
@@ -2100,33 +2136,35 @@
       </c>
       <c r="K7" s="8" t="n">
         <f aca="false">INDEX(A:A, COUNTA(B:B)-7+ROW())</f>
-        <v>46178</v>
+        <v>46211</v>
       </c>
       <c r="L7" s="9" t="n">
         <f aca="false">INDEX(B:B, COUNTA(B:B)-7+ROW())</f>
-        <v>76.6</v>
+        <v>76.7</v>
       </c>
       <c r="M7" s="10" t="n">
         <f aca="false">INDEX(G:G, COUNTA(B:B)-7+ROW())</f>
-        <v>0</v>
+        <v>76.9375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="n">
         <v>46182</v>
       </c>
-      <c r="B8" s="6"/>
+      <c r="B8" s="6" t="n">
+        <v>75.6</v>
+      </c>
       <c r="C8" s="11" t="n">
         <f aca="false">B8-B7</f>
-        <v>0</v>
+        <v>-0.600000000000009</v>
       </c>
       <c r="D8" s="3" t="n">
         <f aca="false">B8*2.204623</f>
-        <v>0</v>
+        <v>166.6694988</v>
       </c>
       <c r="E8" s="7" t="n">
         <f aca="false">C8*2.204623</f>
-        <v>0</v>
+        <v>-1.32277380000002</v>
       </c>
       <c r="F8" s="4" t="n">
         <f aca="false">A8</f>
@@ -2138,18 +2176,20 @@
       <c r="A9" s="5" t="n">
         <v>46183</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="6" t="n">
+        <v>75</v>
+      </c>
       <c r="C9" s="11" t="n">
         <f aca="false">B9-B8</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D9" s="3" t="n">
         <f aca="false">B9*2.204623</f>
-        <v>0</v>
+        <v>165.346725</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">C9*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F9" s="4" t="n">
         <f aca="false">A9</f>
@@ -2157,11 +2197,13 @@
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">AVERAGE(B2:B9)</f>
-        <v>77.0333333333333</v>
-      </c>
-      <c r="H9" s="6"/>
+        <v>76.5375</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="I9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1000</v>
@@ -2171,18 +2213,20 @@
       <c r="A10" s="5" t="n">
         <v>46184</v>
       </c>
-      <c r="B10" s="6"/>
+      <c r="B10" s="6" t="n">
+        <v>74.4</v>
+      </c>
       <c r="C10" s="11" t="n">
         <f aca="false">B10-B9</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D10" s="3" t="n">
         <f aca="false">B10*2.204623</f>
-        <v>0</v>
+        <v>164.0239512</v>
       </c>
       <c r="E10" s="7" t="n">
         <f aca="false">C10*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F10" s="4" t="n">
         <f aca="false">A10</f>
@@ -2190,28 +2234,33 @@
       </c>
       <c r="G10" s="7" t="n">
         <f aca="false">AVERAGE(B3:B10)</f>
-        <v>76.8</v>
-      </c>
-      <c r="H10" s="6"/>
+        <v>76.15</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="I10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="J10" s="3" t="e">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
-        <v>#VALUE!</v>
+        <v>48.6000000000001</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="n">
         <v>46185</v>
       </c>
+      <c r="B11" s="1" t="n">
+        <v>74.4</v>
+      </c>
       <c r="C11" s="11" t="n">
         <f aca="false">B11-B10</f>
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
         <f aca="false">B11*2.204623</f>
-        <v>0</v>
+        <v>164.0239512</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">C11*2.204623</f>
@@ -2223,20 +2272,26 @@
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">AVERAGE(B4:B11)</f>
-        <v>76.6</v>
+        <v>75.825</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="n">
         <v>46186</v>
       </c>
+      <c r="B12" s="1" t="n">
+        <v>74.4</v>
+      </c>
       <c r="C12" s="11" t="n">
         <f aca="false">B12-B11</f>
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <f aca="false">B12*2.204623</f>
-        <v>0</v>
+        <v>164.0239512</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">C12*2.204623</f>
@@ -2246,147 +2301,174 @@
         <f aca="false">A12</f>
         <v>46186</v>
       </c>
-      <c r="G12" s="7" t="e">
+      <c r="G12" s="7" t="n">
         <f aca="false">AVERAGE(B5:B12)</f>
-        <v>#DIV/0!</v>
+        <v>75.55</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
         <v>46187</v>
       </c>
+      <c r="B13" s="1" t="n">
+        <v>74.2</v>
+      </c>
       <c r="C13" s="11" t="n">
         <f aca="false">B13-B12</f>
-        <v>0</v>
+        <v>-0.200000000000003</v>
       </c>
       <c r="D13" s="3" t="n">
         <f aca="false">B13*2.204623</f>
-        <v>0</v>
+        <v>163.5830266</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">C13*2.204623</f>
-        <v>0</v>
+        <v>-0.440924600000006</v>
       </c>
       <c r="F13" s="4" t="n">
         <f aca="false">A13</f>
         <v>46187</v>
       </c>
-      <c r="G13" s="7" t="e">
+      <c r="G13" s="7" t="n">
         <f aca="false">AVERAGE(B6:B13)</f>
-        <v>#DIV/0!</v>
+        <v>75.2875</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="n">
         <v>46188</v>
       </c>
+      <c r="B14" s="1" t="n">
+        <v>75.9</v>
+      </c>
       <c r="C14" s="11" t="n">
         <f aca="false">B14-B13</f>
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="D14" s="3" t="n">
         <f aca="false">B14*2.204623</f>
-        <v>0</v>
+        <v>167.3308857</v>
       </c>
       <c r="E14" s="7" t="n">
         <f aca="false">C14*2.204623</f>
-        <v>0</v>
+        <v>3.74785910000001</v>
       </c>
       <c r="F14" s="4" t="n">
         <f aca="false">A14</f>
         <v>46188</v>
       </c>
-      <c r="G14" s="7" t="e">
+      <c r="G14" s="7" t="n">
         <f aca="false">AVERAGE(B7:B14)</f>
-        <v>#DIV/0!</v>
+        <v>75.0125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="n">
         <v>46189</v>
       </c>
+      <c r="B15" s="1" t="n">
+        <v>75.1</v>
+      </c>
       <c r="C15" s="11" t="n">
         <f aca="false">B15-B14</f>
-        <v>0</v>
+        <v>-0.800000000000011</v>
       </c>
       <c r="D15" s="3" t="n">
         <f aca="false">B15*2.204623</f>
-        <v>0</v>
+        <v>165.5671873</v>
       </c>
       <c r="E15" s="7" t="n">
         <f aca="false">C15*2.204623</f>
-        <v>0</v>
+        <v>-1.76369840000003</v>
       </c>
       <c r="F15" s="4" t="n">
         <f aca="false">A15</f>
         <v>46189</v>
       </c>
-      <c r="G15" s="7" t="e">
+      <c r="G15" s="7" t="n">
         <f aca="false">AVERAGE(B8:B15)</f>
-        <v>#DIV/0!</v>
+        <v>74.875</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="n">
         <v>46190</v>
       </c>
+      <c r="B16" s="1" t="n">
+        <v>74.4</v>
+      </c>
       <c r="C16" s="11" t="n">
         <f aca="false">B16-B15</f>
-        <v>0</v>
+        <v>-0.699999999999989</v>
       </c>
       <c r="D16" s="3" t="n">
         <f aca="false">B16*2.204623</f>
-        <v>0</v>
+        <v>164.0239512</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">C16*2.204623</f>
-        <v>0</v>
+        <v>-1.54323609999998</v>
       </c>
       <c r="F16" s="4" t="n">
         <f aca="false">A16</f>
         <v>46190</v>
       </c>
-      <c r="G16" s="7" t="e">
+      <c r="G16" s="7" t="n">
         <f aca="false">AVERAGE(B9:B16)</f>
-        <v>#DIV/0!</v>
+        <v>74.725</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="n">
         <v>46191</v>
       </c>
+      <c r="B17" s="1" t="n">
+        <v>74.6</v>
+      </c>
       <c r="C17" s="11" t="n">
         <f aca="false">B17-B16</f>
-        <v>0</v>
+        <v>0.199999999999989</v>
       </c>
       <c r="D17" s="3" t="n">
         <f aca="false">B17*2.204623</f>
-        <v>0</v>
+        <v>164.4648758</v>
       </c>
       <c r="E17" s="7" t="n">
         <f aca="false">C17*2.204623</f>
-        <v>0</v>
+        <v>0.440924599999975</v>
       </c>
       <c r="F17" s="4" t="n">
         <f aca="false">A17</f>
         <v>46191</v>
       </c>
-      <c r="G17" s="7" t="e">
+      <c r="G17" s="7" t="n">
         <f aca="false">AVERAGE(B10:B17)</f>
-        <v>#DIV/0!</v>
+        <v>74.675</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="n">
         <v>46192</v>
       </c>
+      <c r="B18" s="1" t="n">
+        <v>74.6</v>
+      </c>
       <c r="C18" s="11" t="n">
         <f aca="false">B18-B17</f>
         <v>0</v>
       </c>
       <c r="D18" s="3" t="n">
         <f aca="false">B18*2.204623</f>
-        <v>0</v>
+        <v>164.4648758</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">C18*2.204623</f>
@@ -2396,34 +2478,37 @@
         <f aca="false">A18</f>
         <v>46192</v>
       </c>
-      <c r="G18" s="7" t="e">
+      <c r="G18" s="7" t="n">
         <f aca="false">AVERAGE(B11:B18)</f>
-        <v>#DIV/0!</v>
+        <v>74.7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="n">
         <v>46193</v>
       </c>
+      <c r="B19" s="1" t="n">
+        <v>73.9</v>
+      </c>
       <c r="C19" s="11" t="n">
         <f aca="false">B19-B18</f>
-        <v>0</v>
+        <v>-0.699999999999989</v>
       </c>
       <c r="D19" s="3" t="n">
         <f aca="false">B19*2.204623</f>
-        <v>0</v>
+        <v>162.9216397</v>
       </c>
       <c r="E19" s="7" t="n">
         <f aca="false">C19*2.204623</f>
-        <v>0</v>
+        <v>-1.54323609999998</v>
       </c>
       <c r="F19" s="4" t="n">
         <f aca="false">A19</f>
         <v>46193</v>
       </c>
-      <c r="G19" s="7" t="e">
+      <c r="G19" s="7" t="n">
         <f aca="false">AVERAGE(B12:B19)</f>
-        <v>#DIV/0!</v>
+        <v>74.6375</v>
       </c>
       <c r="H19" s="5"/>
     </row>
@@ -2431,25 +2516,28 @@
       <c r="A20" s="5" t="n">
         <v>46194</v>
       </c>
+      <c r="B20" s="1" t="n">
+        <v>77.3</v>
+      </c>
       <c r="C20" s="11" t="n">
         <f aca="false">B20-B19</f>
-        <v>0</v>
+        <v>3.39999999999999</v>
       </c>
       <c r="D20" s="3" t="n">
         <f aca="false">B20*2.204623</f>
-        <v>0</v>
+        <v>170.4173579</v>
       </c>
       <c r="E20" s="7" t="n">
         <f aca="false">C20*2.204623</f>
-        <v>0</v>
+        <v>7.49571819999998</v>
       </c>
       <c r="F20" s="4" t="n">
         <f aca="false">A20</f>
         <v>46194</v>
       </c>
-      <c r="G20" s="7" t="e">
+      <c r="G20" s="7" t="n">
         <f aca="false">AVERAGE(B13:B20)</f>
-        <v>#DIV/0!</v>
+        <v>75</v>
       </c>
       <c r="H20" s="5"/>
     </row>
@@ -2457,25 +2545,28 @@
       <c r="A21" s="5" t="n">
         <v>46195</v>
       </c>
+      <c r="B21" s="1" t="n">
+        <v>76</v>
+      </c>
       <c r="C21" s="11" t="n">
         <f aca="false">B21-B20</f>
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="D21" s="3" t="n">
         <f aca="false">B21*2.204623</f>
-        <v>0</v>
+        <v>167.551348</v>
       </c>
       <c r="E21" s="7" t="n">
         <f aca="false">C21*2.204623</f>
-        <v>0</v>
+        <v>-2.86600989999999</v>
       </c>
       <c r="F21" s="4" t="n">
         <f aca="false">A21</f>
         <v>46195</v>
       </c>
-      <c r="G21" s="7" t="e">
+      <c r="G21" s="7" t="n">
         <f aca="false">AVERAGE(B14:B21)</f>
-        <v>#DIV/0!</v>
+        <v>75.225</v>
       </c>
       <c r="H21" s="5"/>
     </row>
@@ -2483,25 +2574,28 @@
       <c r="A22" s="5" t="n">
         <v>46196</v>
       </c>
+      <c r="B22" s="1" t="n">
+        <v>75.5</v>
+      </c>
       <c r="C22" s="11" t="n">
         <f aca="false">B22-B21</f>
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="D22" s="3" t="n">
         <f aca="false">B22*2.204623</f>
-        <v>0</v>
+        <v>166.4490365</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">C22*2.204623</f>
-        <v>0</v>
+        <v>-1.1023115</v>
       </c>
       <c r="F22" s="4" t="n">
         <f aca="false">A22</f>
         <v>46196</v>
       </c>
-      <c r="G22" s="7" t="e">
+      <c r="G22" s="7" t="n">
         <f aca="false">AVERAGE(B15:B22)</f>
-        <v>#DIV/0!</v>
+        <v>75.175</v>
       </c>
       <c r="H22" s="5"/>
     </row>
@@ -2509,51 +2603,59 @@
       <c r="A23" s="5" t="n">
         <v>46197</v>
       </c>
+      <c r="B23" s="1" t="n">
+        <v>74.9</v>
+      </c>
       <c r="C23" s="11" t="n">
         <f aca="false">B23-B22</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D23" s="3" t="n">
         <f aca="false">B23*2.204623</f>
-        <v>0</v>
+        <v>165.1262627</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">C23*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F23" s="4" t="n">
         <f aca="false">A23</f>
         <v>46197</v>
       </c>
-      <c r="G23" s="7" t="e">
+      <c r="G23" s="7" t="n">
         <f aca="false">AVERAGE(B16:B23)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H23" s="5"/>
+        <v>75.15</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
         <v>46198</v>
       </c>
+      <c r="B24" s="1" t="n">
+        <v>75.7</v>
+      </c>
       <c r="C24" s="11" t="n">
         <f aca="false">B24-B23</f>
-        <v>0</v>
+        <v>0.799999999999997</v>
       </c>
       <c r="D24" s="3" t="n">
         <f aca="false">B24*2.204623</f>
-        <v>0</v>
+        <v>166.8899611</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">C24*2.204623</f>
-        <v>0</v>
+        <v>1.76369839999999</v>
       </c>
       <c r="F24" s="4" t="n">
         <f aca="false">A24</f>
         <v>46198</v>
       </c>
-      <c r="G24" s="7" t="e">
+      <c r="G24" s="7" t="n">
         <f aca="false">AVERAGE(B17:B24)</f>
-        <v>#DIV/0!</v>
+        <v>75.3125</v>
       </c>
       <c r="H24" s="5"/>
     </row>
@@ -2561,51 +2663,59 @@
       <c r="A25" s="5" t="n">
         <v>46199</v>
       </c>
+      <c r="B25" s="1" t="n">
+        <v>74.5</v>
+      </c>
       <c r="C25" s="11" t="n">
         <f aca="false">B25-B24</f>
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="D25" s="3" t="n">
         <f aca="false">B25*2.204623</f>
-        <v>0</v>
+        <v>164.2444135</v>
       </c>
       <c r="E25" s="7" t="n">
         <f aca="false">C25*2.204623</f>
-        <v>0</v>
+        <v>-2.64554760000001</v>
       </c>
       <c r="F25" s="4" t="n">
         <f aca="false">A25</f>
         <v>46199</v>
       </c>
-      <c r="G25" s="7" t="e">
+      <c r="G25" s="7" t="n">
         <f aca="false">AVERAGE(B18:B25)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H25" s="5"/>
+        <v>75.3</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
         <v>46200</v>
       </c>
+      <c r="B26" s="1" t="n">
+        <v>78.3</v>
+      </c>
       <c r="C26" s="11" t="n">
         <f aca="false">B26-B25</f>
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="D26" s="3" t="n">
         <f aca="false">B26*2.204623</f>
-        <v>0</v>
+        <v>172.6219809</v>
       </c>
       <c r="E26" s="7" t="n">
         <f aca="false">C26*2.204623</f>
-        <v>0</v>
+        <v>8.3775674</v>
       </c>
       <c r="F26" s="4" t="n">
         <f aca="false">A26</f>
         <v>46200</v>
       </c>
-      <c r="G26" s="7" t="e">
+      <c r="G26" s="7" t="n">
         <f aca="false">AVERAGE(B19:B26)</f>
-        <v>#DIV/0!</v>
+        <v>75.7625</v>
       </c>
       <c r="H26" s="5"/>
     </row>
@@ -2613,25 +2723,28 @@
       <c r="A27" s="5" t="n">
         <v>46201</v>
       </c>
+      <c r="B27" s="1" t="n">
+        <v>77.7</v>
+      </c>
       <c r="C27" s="11" t="n">
         <f aca="false">B27-B26</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D27" s="3" t="n">
         <f aca="false">B27*2.204623</f>
-        <v>0</v>
+        <v>171.2992071</v>
       </c>
       <c r="E27" s="7" t="n">
         <f aca="false">C27*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F27" s="4" t="n">
         <f aca="false">A27</f>
         <v>46201</v>
       </c>
-      <c r="G27" s="7" t="e">
+      <c r="G27" s="7" t="n">
         <f aca="false">AVERAGE(B20:B27)</f>
-        <v>#DIV/0!</v>
+        <v>76.2375</v>
       </c>
       <c r="H27" s="5"/>
     </row>
@@ -2639,25 +2752,28 @@
       <c r="A28" s="5" t="n">
         <v>46202</v>
       </c>
+      <c r="B28" s="1" t="n">
+        <v>77.8</v>
+      </c>
       <c r="C28" s="11" t="n">
         <f aca="false">B28-B27</f>
-        <v>0</v>
+        <v>0.0999999999999943</v>
       </c>
       <c r="D28" s="3" t="n">
         <f aca="false">B28*2.204623</f>
-        <v>0</v>
+        <v>171.5196694</v>
       </c>
       <c r="E28" s="7" t="n">
         <f aca="false">C28*2.204623</f>
-        <v>0</v>
+        <v>0.220462299999987</v>
       </c>
       <c r="F28" s="4" t="n">
         <f aca="false">A28</f>
         <v>46202</v>
       </c>
-      <c r="G28" s="7" t="e">
+      <c r="G28" s="7" t="n">
         <f aca="false">AVERAGE(B21:B28)</f>
-        <v>#DIV/0!</v>
+        <v>76.3</v>
       </c>
       <c r="H28" s="5"/>
     </row>
@@ -2665,25 +2781,28 @@
       <c r="A29" s="5" t="n">
         <v>46203</v>
       </c>
+      <c r="B29" s="1" t="n">
+        <v>76.5</v>
+      </c>
       <c r="C29" s="11" t="n">
         <f aca="false">B29-B28</f>
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="D29" s="3" t="n">
         <f aca="false">B29*2.204623</f>
-        <v>0</v>
+        <v>168.6536595</v>
       </c>
       <c r="E29" s="7" t="n">
         <f aca="false">C29*2.204623</f>
-        <v>0</v>
+        <v>-2.86600989999999</v>
       </c>
       <c r="F29" s="4" t="n">
         <f aca="false">A29</f>
         <v>46203</v>
       </c>
-      <c r="G29" s="7" t="e">
+      <c r="G29" s="7" t="n">
         <f aca="false">AVERAGE(B22:B29)</f>
-        <v>#DIV/0!</v>
+        <v>76.3625</v>
       </c>
       <c r="H29" s="5"/>
     </row>
@@ -2691,25 +2810,28 @@
       <c r="A30" s="5" t="n">
         <v>46204</v>
       </c>
+      <c r="B30" s="1" t="n">
+        <v>76.9</v>
+      </c>
       <c r="C30" s="11" t="n">
         <f aca="false">B30-B29</f>
-        <v>0</v>
+        <v>0.400000000000006</v>
       </c>
       <c r="D30" s="3" t="n">
         <f aca="false">B30*2.204623</f>
-        <v>0</v>
+        <v>169.5355087</v>
       </c>
       <c r="E30" s="7" t="n">
         <f aca="false">C30*2.204623</f>
-        <v>0</v>
+        <v>0.881849200000013</v>
       </c>
       <c r="F30" s="4" t="n">
         <f aca="false">A30</f>
         <v>46204</v>
       </c>
-      <c r="G30" s="7" t="e">
+      <c r="G30" s="7" t="n">
         <f aca="false">AVERAGE(B23:B30)</f>
-        <v>#DIV/0!</v>
+        <v>76.5375</v>
       </c>
       <c r="H30" s="5"/>
       <c r="L30" s="6"/>
@@ -2718,25 +2840,28 @@
       <c r="A31" s="5" t="n">
         <v>46205</v>
       </c>
+      <c r="B31" s="1" t="n">
+        <v>76.3</v>
+      </c>
       <c r="C31" s="11" t="n">
         <f aca="false">B31-B30</f>
-        <v>0</v>
+        <v>-0.600000000000009</v>
       </c>
       <c r="D31" s="3" t="n">
         <f aca="false">B31*2.204623</f>
-        <v>0</v>
+        <v>168.2127349</v>
       </c>
       <c r="E31" s="7" t="n">
         <f aca="false">C31*2.204623</f>
-        <v>0</v>
+        <v>-1.32277380000002</v>
       </c>
       <c r="F31" s="4" t="n">
         <f aca="false">A31</f>
         <v>46205</v>
       </c>
-      <c r="G31" s="7" t="e">
+      <c r="G31" s="7" t="n">
         <f aca="false">AVERAGE(B24:B31)</f>
-        <v>#DIV/0!</v>
+        <v>76.7125</v>
       </c>
       <c r="H31" s="5"/>
     </row>
@@ -2744,25 +2869,28 @@
       <c r="A32" s="5" t="n">
         <v>46206</v>
       </c>
+      <c r="B32" s="1" t="n">
+        <v>77.3</v>
+      </c>
       <c r="C32" s="11" t="n">
         <f aca="false">B32-B31</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" s="3" t="n">
         <f aca="false">B32*2.204623</f>
-        <v>0</v>
+        <v>170.4173579</v>
       </c>
       <c r="E32" s="7" t="n">
         <f aca="false">C32*2.204623</f>
-        <v>0</v>
+        <v>2.204623</v>
       </c>
       <c r="F32" s="4" t="n">
         <f aca="false">A32</f>
         <v>46206</v>
       </c>
-      <c r="G32" s="7" t="e">
+      <c r="G32" s="7" t="n">
         <f aca="false">AVERAGE(B25:B32)</f>
-        <v>#DIV/0!</v>
+        <v>76.9125</v>
       </c>
       <c r="H32" s="5"/>
     </row>
@@ -2770,25 +2898,28 @@
       <c r="A33" s="5" t="n">
         <v>46207</v>
       </c>
+      <c r="B33" s="1" t="n">
+        <v>76.7</v>
+      </c>
       <c r="C33" s="11" t="n">
         <f aca="false">B33-B32</f>
-        <v>0</v>
+        <v>-0.599999999999994</v>
       </c>
       <c r="D33" s="3" t="n">
         <f aca="false">B33*2.204623</f>
-        <v>0</v>
+        <v>169.0945841</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">C33*2.204623</f>
-        <v>0</v>
+        <v>-1.32277379999999</v>
       </c>
       <c r="F33" s="4" t="n">
         <f aca="false">A33</f>
         <v>46207</v>
       </c>
-      <c r="G33" s="7" t="e">
+      <c r="G33" s="7" t="n">
         <f aca="false">AVERAGE(B26:B33)</f>
-        <v>#DIV/0!</v>
+        <v>77.1875</v>
       </c>
       <c r="H33" s="5"/>
     </row>
@@ -2796,25 +2927,28 @@
       <c r="A34" s="5" t="n">
         <v>46208</v>
       </c>
+      <c r="B34" s="1" t="n">
+        <v>77.7</v>
+      </c>
       <c r="C34" s="11" t="n">
         <f aca="false">B34-B33</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3" t="n">
         <f aca="false">B34*2.204623</f>
-        <v>0</v>
+        <v>171.2992071</v>
       </c>
       <c r="E34" s="7" t="n">
         <f aca="false">C34*2.204623</f>
-        <v>0</v>
+        <v>2.204623</v>
       </c>
       <c r="F34" s="4" t="n">
         <f aca="false">A34</f>
         <v>46208</v>
       </c>
-      <c r="G34" s="7" t="e">
+      <c r="G34" s="7" t="n">
         <f aca="false">AVERAGE(B27:B34)</f>
-        <v>#DIV/0!</v>
+        <v>77.1125</v>
       </c>
       <c r="H34" s="5"/>
     </row>
@@ -2822,203 +2956,662 @@
       <c r="A35" s="5" t="n">
         <v>46209</v>
       </c>
+      <c r="B35" s="1" t="n">
+        <v>77.6</v>
+      </c>
       <c r="C35" s="11" t="n">
         <f aca="false">B35-B34</f>
-        <v>0</v>
+        <v>-0.100000000000009</v>
       </c>
       <c r="D35" s="3" t="n">
         <f aca="false">B35*2.204623</f>
-        <v>0</v>
+        <v>171.0787448</v>
       </c>
       <c r="E35" s="7" t="n">
         <f aca="false">C35*2.204623</f>
-        <v>0</v>
+        <v>-0.220462300000019</v>
       </c>
       <c r="F35" s="4" t="n">
         <f aca="false">A35</f>
         <v>46209</v>
       </c>
-      <c r="G35" s="7" t="e">
+      <c r="G35" s="7" t="n">
         <f aca="false">AVERAGE(B28:B35)</f>
+        <v>77.1</v>
+      </c>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>76.3</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <f aca="false">B36-B35</f>
+        <v>-1.3</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <f aca="false">B36*2.204623</f>
+        <v>168.2127349</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <f aca="false">C36*2.204623</f>
+        <v>-2.86600989999999</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <f aca="false">A36</f>
+        <v>46210</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <f aca="false">AVERAGE(B29:B36)</f>
+        <v>76.9125</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <f aca="false">B37-B36</f>
+        <v>0.400000000000006</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <f aca="false">B37*2.204623</f>
+        <v>169.0945841</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <f aca="false">C37*2.204623</f>
+        <v>0.881849200000013</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <f aca="false">A37</f>
+        <v>46211</v>
+      </c>
+      <c r="G37" s="7" t="n">
+        <f aca="false">AVERAGE(B30:B37)</f>
+        <v>76.9375</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="n">
+        <v>46212</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <f aca="false">B38-B37</f>
+        <v>-76.7</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <f aca="false">B38*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <f aca="false">C38*2.204623</f>
+        <v>-169.0945841</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <f aca="false">A38</f>
+        <v>46212</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <f aca="false">AVERAGE(B31:B38)</f>
+        <v>76.9428571428572</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="n">
+        <v>46213</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <f aca="false">B39-B38</f>
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <f aca="false">B39*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <f aca="false">C39*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <f aca="false">A39</f>
+        <v>46213</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <f aca="false">AVERAGE(B32:B39)</f>
+        <v>77.05</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="n">
+        <v>46214</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <f aca="false">B40-B39</f>
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <f aca="false">B40*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <f aca="false">C40*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <f aca="false">A40</f>
+        <v>46214</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <f aca="false">AVERAGE(B33:B40)</f>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="n">
+        <v>46215</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <f aca="false">B41-B40</f>
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <f aca="false">B41*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <f aca="false">C41*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <f aca="false">A41</f>
+        <v>46215</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <f aca="false">AVERAGE(B34:B41)</f>
+        <v>77.075</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="n">
+        <v>46216</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <f aca="false">B42-B41</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <f aca="false">B42*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <f aca="false">C42*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <f aca="false">A42</f>
+        <v>46216</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <f aca="false">AVERAGE(B35:B42)</f>
+        <v>76.8666666666667</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="n">
+        <v>46217</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <f aca="false">B43-B42</f>
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <f aca="false">B43*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <f aca="false">C43*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <f aca="false">A43</f>
+        <v>46217</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <f aca="false">AVERAGE(B36:B43)</f>
+        <v>76.5</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="n">
+        <v>46218</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <f aca="false">B44-B43</f>
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <f aca="false">B44*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <f aca="false">C44*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <f aca="false">A44</f>
+        <v>46218</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <f aca="false">AVERAGE(B37:B44)</f>
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="n">
+        <v>46219</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <f aca="false">B45-B44</f>
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <f aca="false">B45*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <f aca="false">C45*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <f aca="false">A45</f>
+        <v>46219</v>
+      </c>
+      <c r="G45" s="7" t="e">
+        <f aca="false">AVERAGE(B38:B45)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H35" s="5"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5"/>
-      <c r="C36" s="11"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5"/>
-      <c r="C37" s="11"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="7"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5"/>
-      <c r="C38" s="11"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5"/>
-      <c r="C39" s="11"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="7"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
-      <c r="C40" s="11"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="7"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="C41" s="11"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="7"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5"/>
-      <c r="C42" s="11"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="7"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5"/>
-      <c r="C43" s="11"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="7"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="C44" s="11"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="7"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="C45" s="11"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="7"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
-      <c r="C46" s="11"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="7"/>
+      <c r="A46" s="5" t="n">
+        <v>46220</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <f aca="false">B46-B45</f>
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <f aca="false">B46*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <f aca="false">C46*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <f aca="false">A46</f>
+        <v>46220</v>
+      </c>
+      <c r="G46" s="7" t="e">
+        <f aca="false">AVERAGE(B39:B46)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
-      <c r="C47" s="11"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="7"/>
+      <c r="A47" s="5" t="n">
+        <v>46221</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <f aca="false">B47-B46</f>
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <f aca="false">B47*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <f aca="false">C47*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <f aca="false">A47</f>
+        <v>46221</v>
+      </c>
+      <c r="G47" s="7" t="e">
+        <f aca="false">AVERAGE(B40:B47)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="C48" s="11"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="7"/>
+      <c r="A48" s="5" t="n">
+        <v>46222</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <f aca="false">B48-B47</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <f aca="false">B48*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <f aca="false">C48*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <f aca="false">A48</f>
+        <v>46222</v>
+      </c>
+      <c r="G48" s="7" t="e">
+        <f aca="false">AVERAGE(B41:B48)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5"/>
-      <c r="C49" s="11"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="7"/>
+      <c r="A49" s="5" t="n">
+        <v>46223</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <f aca="false">B49-B48</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <f aca="false">B49*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <f aca="false">C49*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <f aca="false">A49</f>
+        <v>46223</v>
+      </c>
+      <c r="G49" s="7" t="e">
+        <f aca="false">AVERAGE(B42:B49)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5"/>
-      <c r="C50" s="11"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="7"/>
+      <c r="A50" s="5" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <f aca="false">B50-B49</f>
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <f aca="false">B50*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <f aca="false">C50*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <f aca="false">A50</f>
+        <v>46224</v>
+      </c>
+      <c r="G50" s="7" t="e">
+        <f aca="false">AVERAGE(B43:B50)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5"/>
-      <c r="C51" s="11"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="7"/>
+      <c r="A51" s="5" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <f aca="false">B51-B50</f>
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <f aca="false">B51*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <f aca="false">C51*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <f aca="false">A51</f>
+        <v>46225</v>
+      </c>
+      <c r="G51" s="7" t="e">
+        <f aca="false">AVERAGE(B44:B51)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5"/>
-      <c r="C52" s="11"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="7"/>
+      <c r="A52" s="5" t="n">
+        <v>46226</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <f aca="false">B52-B51</f>
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <f aca="false">B52*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <f aca="false">C52*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <f aca="false">A52</f>
+        <v>46226</v>
+      </c>
+      <c r="G52" s="7" t="e">
+        <f aca="false">AVERAGE(B45:B52)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5"/>
-      <c r="C53" s="11"/>
-      <c r="E53" s="7"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="7"/>
+      <c r="A53" s="5" t="n">
+        <v>46227</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <f aca="false">B53-B52</f>
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <f aca="false">B53*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <f aca="false">C53*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <f aca="false">A53</f>
+        <v>46227</v>
+      </c>
+      <c r="G53" s="7" t="e">
+        <f aca="false">AVERAGE(B46:B53)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5"/>
-      <c r="C54" s="11"/>
-      <c r="E54" s="7"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="7"/>
+      <c r="A54" s="5" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <f aca="false">B54-B53</f>
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <f aca="false">B54*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <f aca="false">C54*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <f aca="false">A54</f>
+        <v>46228</v>
+      </c>
+      <c r="G54" s="7" t="e">
+        <f aca="false">AVERAGE(B47:B54)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5"/>
-      <c r="C55" s="11"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="7"/>
+      <c r="A55" s="5" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <f aca="false">B55-B54</f>
+        <v>0</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <f aca="false">B55*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <f aca="false">C55*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <f aca="false">A55</f>
+        <v>46229</v>
+      </c>
+      <c r="G55" s="7" t="e">
+        <f aca="false">AVERAGE(B48:B55)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5"/>
-      <c r="C56" s="11"/>
-      <c r="E56" s="7"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="7"/>
+      <c r="A56" s="5" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <f aca="false">B56-B55</f>
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <f aca="false">B56*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <f aca="false">C56*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <f aca="false">A56</f>
+        <v>46230</v>
+      </c>
+      <c r="G56" s="7" t="e">
+        <f aca="false">AVERAGE(B49:B56)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5"/>
-      <c r="C57" s="11"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="7"/>
+      <c r="A57" s="5" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <f aca="false">B57-B56</f>
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <f aca="false">B57*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <f aca="false">C57*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <f aca="false">A57</f>
+        <v>46231</v>
+      </c>
+      <c r="G57" s="7" t="e">
+        <f aca="false">AVERAGE(B50:B57)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
+      <c r="A58" s="5" t="n">
+        <v>46232</v>
+      </c>
       <c r="B58" s="6"/>
-      <c r="C58" s="11"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="7"/>
+      <c r="C58" s="11" t="n">
+        <f aca="false">B58-B57</f>
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <f aca="false">B58*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <f aca="false">C58*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <f aca="false">A58</f>
+        <v>46232</v>
+      </c>
+      <c r="G58" s="7" t="e">
+        <f aca="false">AVERAGE(B51:B58)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5"/>
-      <c r="C59" s="11"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="7"/>
+      <c r="A59" s="5" t="n">
+        <v>46233</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <f aca="false">B59-B58</f>
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <f aca="false">B59*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <f aca="false">C59*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <f aca="false">A59</f>
+        <v>46233</v>
+      </c>
+      <c r="G59" s="7" t="e">
+        <f aca="false">AVERAGE(B52:B59)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5"/>
-      <c r="C60" s="11"/>
-      <c r="E60" s="7"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="7"/>
+      <c r="A60" s="5" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <f aca="false">B60-B59</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <f aca="false">B60*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <f aca="false">C60*2.204623</f>
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <f aca="false">A60</f>
+        <v>46234</v>
+      </c>
+      <c r="G60" s="7" t="e">
+        <f aca="false">AVERAGE(B53:B60)</f>
+        <v>#DIV/0!</v>
+      </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -3544,6 +4137,106 @@
               <xm:f>Sheet1!B34</xm:f>
               <xm:sqref>A35</xm:sqref>
             </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B35</xm:f>
+              <xm:sqref>A36</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B36</xm:f>
+              <xm:sqref>A37</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B37</xm:f>
+              <xm:sqref>A38</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B38</xm:f>
+              <xm:sqref>A39</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B39</xm:f>
+              <xm:sqref>A40</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B40</xm:f>
+              <xm:sqref>A41</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B41</xm:f>
+              <xm:sqref>A42</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B42</xm:f>
+              <xm:sqref>A43</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B43</xm:f>
+              <xm:sqref>A44</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B44</xm:f>
+              <xm:sqref>A45</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B45</xm:f>
+              <xm:sqref>A46</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B46</xm:f>
+              <xm:sqref>A47</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B47</xm:f>
+              <xm:sqref>A48</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B48</xm:f>
+              <xm:sqref>A49</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B49</xm:f>
+              <xm:sqref>A50</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B50</xm:f>
+              <xm:sqref>A51</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B51</xm:f>
+              <xm:sqref>A52</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B52</xm:f>
+              <xm:sqref>A53</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B53</xm:f>
+              <xm:sqref>A54</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B54</xm:f>
+              <xm:sqref>A55</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B55</xm:f>
+              <xm:sqref>A56</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B56</xm:f>
+              <xm:sqref>A57</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B57</xm:f>
+              <xm:sqref>A58</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B58</xm:f>
+              <xm:sqref>A59</xm:sqref>
+            </x14:sparkline>
+            <x14:sparkline>
+              <xm:f>Sheet1!B59</xm:f>
+              <xm:sqref>A60</xm:sqref>
+            </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
       </x14:sparklineGroups>
@@ -3593,7 +4286,7 @@
         <v>0</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>2</v>
@@ -3710,7 +4403,7 @@
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
@@ -3836,7 +4529,7 @@
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>70</v>
@@ -3907,10 +4600,10 @@
         <v>77.0125</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="3" t="n">
         <v>1000</v>
@@ -3944,10 +4637,10 @@
         <v>76.9875</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J10" s="3" t="n">
         <f aca="false">((I5 - I7) * 7000) / J9</f>
@@ -3982,7 +4675,7 @@
         <v>77.05</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4013,7 +4706,7 @@
         <v>77.2125</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4212,7 +4905,7 @@
         <v>77.7</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4411,7 +5104,7 @@
         <v>76.9</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4611,7 +5304,7 @@
         <v>75.95</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4810,7 +5503,7 @@
         <v>75.7</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,7 +5702,7 @@
         <v>75.2375</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5152,7 +5845,7 @@
         <v>74.8625</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5183,7 +5876,7 @@
         <v>74.9125</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5214,7 +5907,7 @@
         <v>75.025</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5245,7 +5938,7 @@
         <v>75.125</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5276,7 +5969,7 @@
         <v>75.05</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5335,7 +6028,7 @@
         <v>75.3</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5422,7 +6115,7 @@
         <v>75.7</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5621,7 +6314,7 @@
         <v>75.3875</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5820,7 +6513,7 @@
         <v>74.675</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5935,7 +6628,7 @@
         <v>75.0125</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5966,7 +6659,7 @@
         <v>75.075</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I80" s="6"/>
     </row>
@@ -5998,7 +6691,7 @@
         <v>75.3</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6029,7 +6722,7 @@
         <v>75.5625</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6060,7 +6753,7 @@
         <v>75.6875</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6091,7 +6784,7 @@
         <v>75.6125</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6122,7 +6815,7 @@
         <v>75.6125</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6153,7 +6846,7 @@
         <v>75.7875</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6976,7 +7669,7 @@
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="6" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I4" s="12" t="n">
         <f aca="true">MEDIAN(OFFSET(B1, COUNTA(B:B)-7, 0, 7))</f>
@@ -7064,7 +7757,7 @@
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I6" s="3" t="n">
         <f aca="false">I5-I8</f>
@@ -7111,7 +7804,7 @@
         <v>85.8571428571429</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I7" s="3" t="n">
         <f aca="false">102-I5</f>
@@ -7158,7 +7851,7 @@
         <v>85.7857142857143</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>75</v>
